--- a/reference/VT Rolling Audit/VT_Municipalities.xlsx
+++ b/reference/VT Rolling Audit/VT_Municipalities.xlsx
@@ -504,12 +504,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Every Vermont municipality in the repo: 235 towns, 10 cities, 30 incorporated villages (275 total, Census 2022), with county, jurisdiction ID, website on file, and charter/code backfill status. VLCT's current (Apr. 2026) count is 237 towns / 28 villages -- a two-place classification drift against the Census 2022 seed, flagged for reconciliation in backfill (see Sources).</t>
+          <t>Every Vermont municipality in the repo: 237 towns, 10 cities, 31 active incorporated villages (278 total), with county, jurisdiction ID, website on file, and charter/code backfill status. The Census 2022 seed (235 / 10 / 30 = 275) was reconciled place-by-place on 2026-10-16 against the official Vermont.gov Towns &amp; Cities explorer and the SOS/VSARA List of Incorporated Villages: Bloomfield and Sudbury towns and Jericho and Westbury villages added; Lyndonville village retired (merged into the Town of Lyndon, Act M-14). VLCT's headline count (237 / 10 / 28) still differs on villages by 3, unexplained in its document; the SOS list governs. Two SOS-listed villages are inactive and excluded: Groton (town assumed functions 1965/67) and Townshend (inactive since 1961).</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>275 municipalities seeded (repo split: 235 towns / 10 cities / 30 villages); charters &amp; code links = Needs Research.</t>
+          <t>278 municipalities (repo split: 237 towns / 10 cities / 31 villages); charters &amp; code links = Needs Research.</t>
         </is>
       </c>
     </row>
@@ -1774,7 +1774,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>30 in the Census 2022 repo seed (VLCT current count: 28 -- reconcile)</t>
+          <t>31 active incorporated villages per the SOS/VSARA list (33 listed incl. 2 inactive: Groton, Townshend; VLCT headline count is 28, definitional difference unresolved)</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1873,7 +1873,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J276"/>
+  <dimension ref="A1:J279"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -3024,7 +3024,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Bolton</t>
+          <t>Bloomfield</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3034,17 +3034,17 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Chittenden</t>
+          <t>Essex</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>ocd-jurisdiction/country:us/state:vt/place:bolton/government</t>
+          <t>ocd-jurisdiction/country:us/state:vt/place:bloomfield/government</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>http://www.townofboltonvt.com</t>
+          <t>Needs Research</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -3064,14 +3064,14 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>Seeded from repo jurisdiction file (Census 2022 Census of Governments). Charter chapter in Title 24 Appendix V.S.A. and code link to be backfilled from the Vermont Legislature municipal charters index and the official municipal website.</t>
+          <t>Added 2026-10-16 (issue #163 fix): missing from the Census 2022 seed; verified on the official Vermont.gov Towns &amp; Cities explorer. Charter/code/website backfill as per sheet.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Bradford</t>
+          <t>Bolton</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3081,17 +3081,17 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Orange</t>
+          <t>Chittenden</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>ocd-jurisdiction/country:us/state:vt/place:bradford/government</t>
+          <t>ocd-jurisdiction/country:us/state:vt/place:bolton/government</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>http://www.bradfordvt.us/</t>
+          <t>http://www.townofboltonvt.com</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -3118,7 +3118,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Braintree</t>
+          <t>Bradford</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3133,12 +3133,12 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>ocd-jurisdiction/country:us/state:vt/place:braintree/government</t>
+          <t>ocd-jurisdiction/country:us/state:vt/place:bradford/government</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>http://www.braintreevt.com/</t>
+          <t>http://www.bradfordvt.us/</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -3165,7 +3165,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Brandon</t>
+          <t>Braintree</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3175,17 +3175,17 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Rutland</t>
+          <t>Orange</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>ocd-jurisdiction/country:us/state:vt/place:brandon/government</t>
+          <t>ocd-jurisdiction/country:us/state:vt/place:braintree/government</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>http://www.town.brandon.vt.us/</t>
+          <t>http://www.braintreevt.com/</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -3212,7 +3212,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Brattleboro</t>
+          <t>Brandon</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3222,17 +3222,17 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Windham</t>
+          <t>Rutland</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>ocd-jurisdiction/country:us/state:vt/place:brattleboro/government</t>
+          <t>ocd-jurisdiction/country:us/state:vt/place:brandon/government</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>http://www.brattleboro.org</t>
+          <t>http://www.town.brandon.vt.us/</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -3259,7 +3259,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Bridgewater</t>
+          <t>Brattleboro</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3269,17 +3269,17 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Windsor</t>
+          <t>Windham</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>ocd-jurisdiction/country:us/state:vt/place:bridgewater/government</t>
+          <t>ocd-jurisdiction/country:us/state:vt/place:brattleboro/government</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Needs Research</t>
+          <t>http://www.brattleboro.org</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -3306,7 +3306,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Bridport</t>
+          <t>Bridgewater</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3316,12 +3316,12 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Addison</t>
+          <t>Windsor</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>ocd-jurisdiction/country:us/state:vt/place:bridport/government</t>
+          <t>ocd-jurisdiction/country:us/state:vt/place:bridgewater/government</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -3353,7 +3353,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Brighton</t>
+          <t>Bridport</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3363,12 +3363,12 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Essex</t>
+          <t>Addison</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>ocd-jurisdiction/country:us/state:vt/place:brighton/government</t>
+          <t>ocd-jurisdiction/country:us/state:vt/place:bridport/government</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -3400,7 +3400,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Bristol</t>
+          <t>Brighton</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3410,17 +3410,17 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Addison</t>
+          <t>Essex</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>ocd-jurisdiction/country:us/state:vt/place:bristol/government</t>
+          <t>ocd-jurisdiction/country:us/state:vt/place:brighton/government</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>http://www.bristolvt.org</t>
+          <t>Needs Research</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -3447,7 +3447,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Brookfield</t>
+          <t>Bristol</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3457,17 +3457,17 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Orange</t>
+          <t>Addison</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>ocd-jurisdiction/country:us/state:vt/place:brookfield/government</t>
+          <t>ocd-jurisdiction/country:us/state:vt/place:bristol/government</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>http://www.brookfieldvt.org/</t>
+          <t>http://www.bristolvt.org</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -3494,7 +3494,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Brookline</t>
+          <t>Brookfield</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3504,17 +3504,17 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Windham</t>
+          <t>Orange</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>ocd-jurisdiction/country:us/state:vt/place:brookline/government</t>
+          <t>ocd-jurisdiction/country:us/state:vt/place:brookfield/government</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>http://www.brooklinevt.com</t>
+          <t>http://www.brookfieldvt.org/</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -3541,7 +3541,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Brownington</t>
+          <t>Brookline</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3551,17 +3551,17 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Orleans</t>
+          <t>Windham</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>ocd-jurisdiction/country:us/state:vt/place:brownington/government</t>
+          <t>ocd-jurisdiction/country:us/state:vt/place:brookline/government</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Needs Research</t>
+          <t>http://www.brooklinevt.com</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -3588,7 +3588,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Brunswick</t>
+          <t>Brownington</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3598,12 +3598,12 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Essex</t>
+          <t>Orleans</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>ocd-jurisdiction/country:us/state:vt/place:brunswick/government</t>
+          <t>ocd-jurisdiction/country:us/state:vt/place:brownington/government</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -3635,7 +3635,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Burke</t>
+          <t>Brunswick</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3645,12 +3645,12 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Caledonia</t>
+          <t>Essex</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>ocd-jurisdiction/country:us/state:vt/place:burke/government</t>
+          <t>ocd-jurisdiction/country:us/state:vt/place:brunswick/government</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -3682,27 +3682,27 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Burlington</t>
+          <t>Burke</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>City</t>
+          <t>Town</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Chittenden</t>
+          <t>Caledonia</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>ocd-jurisdiction/country:us/state:vt/place:burlington/government</t>
+          <t>ocd-jurisdiction/country:us/state:vt/place:burke/government</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>http://www.burlingtonvt.gov</t>
+          <t>Needs Research</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -3729,27 +3729,27 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Cabot</t>
+          <t>Burlington</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Town</t>
+          <t>City</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Washington</t>
+          <t>Chittenden</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>ocd-jurisdiction/country:us/state:vt/place:cabot/government</t>
+          <t>ocd-jurisdiction/country:us/state:vt/place:burlington/government</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>http://www.cabotvt.us</t>
+          <t>http://www.burlingtonvt.gov</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -3776,7 +3776,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Calais</t>
+          <t>Cabot</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3791,12 +3791,12 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>ocd-jurisdiction/country:us/state:vt/place:calais/government</t>
+          <t>ocd-jurisdiction/country:us/state:vt/place:cabot/government</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Needs Research</t>
+          <t>http://www.cabotvt.us</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -3823,7 +3823,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Cambridge</t>
+          <t>Calais</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3833,12 +3833,12 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Lamoille</t>
+          <t>Washington</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>ocd-jurisdiction/country:us/state:vt/place:cambridge-11500/government</t>
+          <t>ocd-jurisdiction/country:us/state:vt/place:calais/government</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -3875,7 +3875,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Village</t>
+          <t>Town</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3885,7 +3885,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>ocd-jurisdiction/country:us/state:vt/place:cambridge/government</t>
+          <t>ocd-jurisdiction/country:us/state:vt/place:cambridge-11500/government</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -3917,27 +3917,27 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Canaan</t>
+          <t>Cambridge</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Town</t>
+          <t>Village</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Essex</t>
+          <t>Lamoille</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>ocd-jurisdiction/country:us/state:vt/place:canaan/government</t>
+          <t>ocd-jurisdiction/country:us/state:vt/place:cambridge/government</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>http://www.canaanvt.org</t>
+          <t>Needs Research</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -3964,7 +3964,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Castleton</t>
+          <t>Canaan</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3974,17 +3974,17 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Rutland</t>
+          <t>Essex</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>ocd-jurisdiction/country:us/state:vt/place:castleton/government</t>
+          <t>ocd-jurisdiction/country:us/state:vt/place:canaan/government</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>http://www.castletonvt.com</t>
+          <t>http://www.canaanvt.org</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -4011,7 +4011,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Cavendish</t>
+          <t>Castleton</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4021,17 +4021,17 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Windsor</t>
+          <t>Rutland</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>ocd-jurisdiction/country:us/state:vt/place:cavendish/government</t>
+          <t>ocd-jurisdiction/country:us/state:vt/place:castleton/government</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Needs Research</t>
+          <t>http://www.castletonvt.com</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -4058,7 +4058,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Charleston</t>
+          <t>Cavendish</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4068,12 +4068,12 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Orleans</t>
+          <t>Windsor</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>ocd-jurisdiction/country:us/state:vt/place:charleston/government</t>
+          <t>ocd-jurisdiction/country:us/state:vt/place:cavendish/government</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -4105,7 +4105,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Charlotte</t>
+          <t>Charleston</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4115,17 +4115,17 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Chittenden</t>
+          <t>Orleans</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>ocd-jurisdiction/country:us/state:vt/place:charlotte/government</t>
+          <t>ocd-jurisdiction/country:us/state:vt/place:charleston/government</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>http://www.charlottevt.org/</t>
+          <t>Needs Research</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -4152,7 +4152,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Charlotte</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4162,17 +4162,17 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Orange</t>
+          <t>Chittenden</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>ocd-jurisdiction/country:us/state:vt/place:chelsea/government</t>
+          <t>ocd-jurisdiction/country:us/state:vt/place:charlotte/government</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>http://www.chelseavt.org</t>
+          <t>http://www.charlottevt.org/</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -4199,7 +4199,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Chester</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4209,17 +4209,17 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Windsor</t>
+          <t>Orange</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>ocd-jurisdiction/country:us/state:vt/place:chester/government</t>
+          <t>ocd-jurisdiction/country:us/state:vt/place:chelsea/government</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Needs Research</t>
+          <t>http://www.chelseavt.org</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -4246,7 +4246,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Chittenden</t>
+          <t>Chester</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4256,12 +4256,12 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Rutland</t>
+          <t>Windsor</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>ocd-jurisdiction/country:us/state:vt/place:chittenden/government</t>
+          <t>ocd-jurisdiction/country:us/state:vt/place:chester/government</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -4293,7 +4293,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Clarendon</t>
+          <t>Chittenden</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4308,12 +4308,12 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>ocd-jurisdiction/country:us/state:vt/place:clarendon/government</t>
+          <t>ocd-jurisdiction/country:us/state:vt/place:chittenden/government</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>http://www.clarendonvt.org</t>
+          <t>Needs Research</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -4340,7 +4340,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Colchester</t>
+          <t>Clarendon</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4350,17 +4350,17 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Chittenden</t>
+          <t>Rutland</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>ocd-jurisdiction/country:us/state:vt/place:colchester/government</t>
+          <t>ocd-jurisdiction/country:us/state:vt/place:clarendon/government</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>http://www.colchestervt.gov</t>
+          <t>http://www.clarendonvt.org</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -4387,7 +4387,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Concord</t>
+          <t>Colchester</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4397,17 +4397,17 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Essex</t>
+          <t>Chittenden</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>ocd-jurisdiction/country:us/state:vt/place:concord/government</t>
+          <t>ocd-jurisdiction/country:us/state:vt/place:colchester/government</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>http://www.concordvt.us</t>
+          <t>http://www.colchestervt.gov</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -4434,7 +4434,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Corinth</t>
+          <t>Concord</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4444,17 +4444,17 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Orange</t>
+          <t>Essex</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>ocd-jurisdiction/country:us/state:vt/place:corinth/government</t>
+          <t>ocd-jurisdiction/country:us/state:vt/place:concord/government</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>http://www.w.w.w.corinthvermont.org</t>
+          <t>http://www.concordvt.us</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -4481,7 +4481,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Cornwall</t>
+          <t>Corinth</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4491,17 +4491,17 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Addison</t>
+          <t>Orange</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>ocd-jurisdiction/country:us/state:vt/place:cornwall/government</t>
+          <t>ocd-jurisdiction/country:us/state:vt/place:corinth/government</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>http://www.cornwall.govoffice2.com</t>
+          <t>http://www.w.w.w.corinthvermont.org</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -4528,7 +4528,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Coventry</t>
+          <t>Cornwall</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4538,17 +4538,17 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Orleans</t>
+          <t>Addison</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>ocd-jurisdiction/country:us/state:vt/place:coventry/government</t>
+          <t>ocd-jurisdiction/country:us/state:vt/place:cornwall/government</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Needs Research</t>
+          <t>http://www.cornwall.govoffice2.com</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -4575,7 +4575,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Craftsbury</t>
+          <t>Coventry</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -4590,7 +4590,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>ocd-jurisdiction/country:us/state:vt/place:craftsbury/government</t>
+          <t>ocd-jurisdiction/country:us/state:vt/place:coventry/government</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -4622,7 +4622,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Danby</t>
+          <t>Craftsbury</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4632,12 +4632,12 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Rutland</t>
+          <t>Orleans</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>ocd-jurisdiction/country:us/state:vt/place:danby/government</t>
+          <t>ocd-jurisdiction/country:us/state:vt/place:craftsbury/government</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -4669,7 +4669,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Danville</t>
+          <t>Danby</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Caledonia</t>
+          <t>Rutland</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>ocd-jurisdiction/country:us/state:vt/place:danville/government</t>
+          <t>ocd-jurisdiction/country:us/state:vt/place:danby/government</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -4716,7 +4716,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Derby</t>
+          <t>Danville</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -4726,17 +4726,17 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Orleans</t>
+          <t>Caledonia</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>ocd-jurisdiction/country:us/state:vt/place:derby/government</t>
+          <t>ocd-jurisdiction/country:us/state:vt/place:danville/government</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>http://www.derbyvt.org</t>
+          <t>Needs Research</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -4763,12 +4763,12 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Derby Center</t>
+          <t>Derby</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Village</t>
+          <t>Town</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -4778,12 +4778,12 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>ocd-jurisdiction/country:us/state:vt/place:derby-center/government</t>
+          <t>ocd-jurisdiction/country:us/state:vt/place:derby/government</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Needs Research</t>
+          <t>http://www.derbyvt.org</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -4810,7 +4810,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Derby Line</t>
+          <t>Derby Center</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -4825,7 +4825,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>ocd-jurisdiction/country:us/state:vt/place:derby-line/government</t>
+          <t>ocd-jurisdiction/country:us/state:vt/place:derby-center/government</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -4857,27 +4857,27 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Dorset</t>
+          <t>Derby Line</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Town</t>
+          <t>Village</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Bennington</t>
+          <t>Orleans</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>ocd-jurisdiction/country:us/state:vt/place:dorset/government</t>
+          <t>ocd-jurisdiction/country:us/state:vt/place:derby-line/government</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>http://www.dorsetvt.org</t>
+          <t>Needs Research</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -4904,7 +4904,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Dover</t>
+          <t>Dorset</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -4914,17 +4914,17 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Windham</t>
+          <t>Bennington</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>ocd-jurisdiction/country:us/state:vt/place:dover/government</t>
+          <t>ocd-jurisdiction/country:us/state:vt/place:dorset/government</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>http://www.doververmont.com</t>
+          <t>http://www.dorsetvt.org</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -4951,7 +4951,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Dummerston</t>
+          <t>Dover</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -4966,12 +4966,12 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>ocd-jurisdiction/country:us/state:vt/place:dummerston/government</t>
+          <t>ocd-jurisdiction/country:us/state:vt/place:dover/government</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>http://www.dummerston.org</t>
+          <t>http://www.doververmont.com</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -4998,7 +4998,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Duxbury</t>
+          <t>Dummerston</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5008,17 +5008,17 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Washington</t>
+          <t>Windham</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>ocd-jurisdiction/country:us/state:vt/place:duxbury/government</t>
+          <t>ocd-jurisdiction/country:us/state:vt/place:dummerston/government</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Needs Research</t>
+          <t>http://www.dummerston.org</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -5045,7 +5045,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>East Haven</t>
+          <t>Duxbury</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Essex</t>
+          <t>Washington</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>ocd-jurisdiction/country:us/state:vt/place:east-haven/government</t>
+          <t>ocd-jurisdiction/country:us/state:vt/place:duxbury/government</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -5092,7 +5092,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>East Montpelier</t>
+          <t>East Haven</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -5102,12 +5102,12 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Washington</t>
+          <t>Essex</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>ocd-jurisdiction/country:us/state:vt/place:east-montpelier/government</t>
+          <t>ocd-jurisdiction/country:us/state:vt/place:east-haven/government</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -5139,7 +5139,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Eden</t>
+          <t>East Montpelier</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -5149,17 +5149,17 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Lamoille</t>
+          <t>Washington</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>ocd-jurisdiction/country:us/state:vt/place:eden/government</t>
+          <t>ocd-jurisdiction/country:us/state:vt/place:east-montpelier/government</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>http://www.edenvt.org</t>
+          <t>Needs Research</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -5186,7 +5186,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Elmore</t>
+          <t>Eden</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -5201,12 +5201,12 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>ocd-jurisdiction/country:us/state:vt/place:elmore/government</t>
+          <t>ocd-jurisdiction/country:us/state:vt/place:eden/government</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>http://www.elmorevt.org</t>
+          <t>http://www.edenvt.org</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -5233,27 +5233,27 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Enosburg Falls</t>
+          <t>Elmore</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Village</t>
+          <t>Town</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Franklin</t>
+          <t>Lamoille</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>ocd-jurisdiction/country:us/state:vt/place:enosburg-falls/government</t>
+          <t>ocd-jurisdiction/country:us/state:vt/place:elmore/government</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Needs Research</t>
+          <t>http://www.elmorevt.org</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -5280,12 +5280,12 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Enosburgh</t>
+          <t>Enosburg Falls</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Town</t>
+          <t>Village</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -5295,7 +5295,7 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>ocd-jurisdiction/country:us/state:vt/place:enosburgh/government</t>
+          <t>ocd-jurisdiction/country:us/state:vt/place:enosburg-falls/government</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -5327,7 +5327,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Essex</t>
+          <t>Enosburgh</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -5337,17 +5337,17 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Chittenden</t>
+          <t>Franklin</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>ocd-jurisdiction/country:us/state:vt/place:essex/government</t>
+          <t>ocd-jurisdiction/country:us/state:vt/place:enosburgh/government</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>http://www.essex.org/</t>
+          <t>Needs Research</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -5374,12 +5374,12 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Essex Junction</t>
+          <t>Essex</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>City</t>
+          <t>Town</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -5389,12 +5389,12 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>ocd-jurisdiction/country:us/state:vt/place:essex-junction/government</t>
+          <t>ocd-jurisdiction/country:us/state:vt/place:essex/government</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>http://www.essexjunction.org/</t>
+          <t>http://www.essex.org/</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -5421,27 +5421,27 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Fair Haven</t>
+          <t>Essex Junction</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Town</t>
+          <t>City</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Rutland</t>
+          <t>Chittenden</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>ocd-jurisdiction/country:us/state:vt/place:fair-haven/government</t>
+          <t>ocd-jurisdiction/country:us/state:vt/place:essex-junction/government</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>http://www.fairhavenvt.org/?page_id166</t>
+          <t>http://www.essexjunction.org/</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -5468,7 +5468,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Fairfax</t>
+          <t>Fair Haven</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -5478,17 +5478,17 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Franklin</t>
+          <t>Rutland</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>ocd-jurisdiction/country:us/state:vt/place:fairfax/government</t>
+          <t>ocd-jurisdiction/country:us/state:vt/place:fair-haven/government</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Needs Research</t>
+          <t>http://www.fairhavenvt.org/?page_id166</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -5515,7 +5515,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Fairfield</t>
+          <t>Fairfax</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -5530,7 +5530,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>ocd-jurisdiction/country:us/state:vt/place:fairfield/government</t>
+          <t>ocd-jurisdiction/country:us/state:vt/place:fairfax/government</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -5562,7 +5562,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Fairlee</t>
+          <t>Fairfield</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -5572,17 +5572,17 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Orange</t>
+          <t>Franklin</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>ocd-jurisdiction/country:us/state:vt/place:fairlee/government</t>
+          <t>ocd-jurisdiction/country:us/state:vt/place:fairfield/government</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>http://www.fairleevt.org</t>
+          <t>Needs Research</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -5609,7 +5609,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Fayston</t>
+          <t>Fairlee</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -5619,17 +5619,17 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Washington</t>
+          <t>Orange</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>ocd-jurisdiction/country:us/state:vt/place:fayston/government</t>
+          <t>ocd-jurisdiction/country:us/state:vt/place:fairlee/government</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>http://www.faystonvt.com</t>
+          <t>http://www.fairleevt.org</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -5656,7 +5656,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Ferrisburgh</t>
+          <t>Fayston</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -5666,17 +5666,17 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Addison</t>
+          <t>Washington</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>ocd-jurisdiction/country:us/state:vt/place:ferrisburgh/government</t>
+          <t>ocd-jurisdiction/country:us/state:vt/place:fayston/government</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>http://www.ferrisburgh.vt.org</t>
+          <t>http://www.faystonvt.com</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -5703,7 +5703,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Fletcher</t>
+          <t>Ferrisburgh</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -5713,17 +5713,17 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Franklin</t>
+          <t>Addison</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>ocd-jurisdiction/country:us/state:vt/place:fletcher/government</t>
+          <t>ocd-jurisdiction/country:us/state:vt/place:ferrisburgh/government</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Needs Research</t>
+          <t>http://www.ferrisburgh.vt.org</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -5750,27 +5750,27 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
+          <t>Fletcher</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Town</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
           <t>Franklin</t>
         </is>
       </c>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>Town</t>
-        </is>
-      </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>Franklin</t>
-        </is>
-      </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>ocd-jurisdiction/country:us/state:vt/place:franklin/government</t>
+          <t>ocd-jurisdiction/country:us/state:vt/place:fletcher/government</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>http://www.franklinvermont.com</t>
+          <t>Needs Research</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -5797,7 +5797,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Georgia</t>
+          <t>Franklin</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -5812,12 +5812,12 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>ocd-jurisdiction/country:us/state:vt/place:georgia/government</t>
+          <t>ocd-jurisdiction/country:us/state:vt/place:franklin/government</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Needs Research</t>
+          <t>http://www.franklinvermont.com</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -5844,7 +5844,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Glover</t>
+          <t>Georgia</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -5854,17 +5854,17 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Orleans</t>
+          <t>Franklin</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>ocd-jurisdiction/country:us/state:vt/place:glover/government</t>
+          <t>ocd-jurisdiction/country:us/state:vt/place:georgia/government</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>http://www.townofglover.com</t>
+          <t>Needs Research</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -5891,7 +5891,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Goshen</t>
+          <t>Glover</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -5901,17 +5901,17 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Addison</t>
+          <t>Orleans</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>ocd-jurisdiction/country:us/state:vt/place:goshen/government</t>
+          <t>ocd-jurisdiction/country:us/state:vt/place:glover/government</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>http://www.goshenvt.org</t>
+          <t>http://www.townofglover.com</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -5938,7 +5938,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Grafton</t>
+          <t>Goshen</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -5948,17 +5948,17 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Windham</t>
+          <t>Addison</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>ocd-jurisdiction/country:us/state:vt/place:grafton/government</t>
+          <t>ocd-jurisdiction/country:us/state:vt/place:goshen/government</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Needs Research</t>
+          <t>http://www.goshenvt.org</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -5985,7 +5985,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Granby</t>
+          <t>Grafton</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -5995,12 +5995,12 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Essex</t>
+          <t>Windham</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>ocd-jurisdiction/country:us/state:vt/place:granby/government</t>
+          <t>ocd-jurisdiction/country:us/state:vt/place:grafton/government</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -6032,7 +6032,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Grand Isle</t>
+          <t>Granby</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -6042,17 +6042,17 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Grand Isle</t>
+          <t>Essex</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>ocd-jurisdiction/country:us/state:vt/place:grand-isle/government</t>
+          <t>ocd-jurisdiction/country:us/state:vt/place:granby/government</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>http://www.grandislevt.org</t>
+          <t>Needs Research</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -6079,7 +6079,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Granville</t>
+          <t>Grand Isle</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -6089,17 +6089,17 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Addison</t>
+          <t>Grand Isle</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>ocd-jurisdiction/country:us/state:vt/place:granville/government</t>
+          <t>ocd-jurisdiction/country:us/state:vt/place:grand-isle/government</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>http://www.granvilletown.org</t>
+          <t>http://www.grandislevt.org</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -6126,7 +6126,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Greensboro</t>
+          <t>Granville</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -6136,17 +6136,17 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Orleans</t>
+          <t>Addison</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>ocd-jurisdiction/country:us/state:vt/place:greensboro/government</t>
+          <t>ocd-jurisdiction/country:us/state:vt/place:granville/government</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>http://greensboro.govoffice.com/</t>
+          <t>http://www.granvilletown.org</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -6173,7 +6173,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Groton</t>
+          <t>Greensboro</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -6183,17 +6183,17 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Caledonia</t>
+          <t>Orleans</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>ocd-jurisdiction/country:us/state:vt/place:groton/government</t>
+          <t>ocd-jurisdiction/country:us/state:vt/place:greensboro/government</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Needs Research</t>
+          <t>http://greensboro.govoffice.com/</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -6220,7 +6220,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Guildhall</t>
+          <t>Groton</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -6230,17 +6230,17 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Essex</t>
+          <t>Caledonia</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>ocd-jurisdiction/country:us/state:vt/place:guildhall/government</t>
+          <t>ocd-jurisdiction/country:us/state:vt/place:groton/government</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>http://www.guildhallvt.org</t>
+          <t>Needs Research</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -6267,7 +6267,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Guilford</t>
+          <t>Guildhall</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -6277,17 +6277,17 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Windham</t>
+          <t>Essex</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>ocd-jurisdiction/country:us/state:vt/place:guilford/government</t>
+          <t>ocd-jurisdiction/country:us/state:vt/place:guildhall/government</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>http://www.guilfordschool.org</t>
+          <t>http://www.guildhallvt.org</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -6314,7 +6314,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Halifax</t>
+          <t>Guilford</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -6329,12 +6329,12 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>ocd-jurisdiction/country:us/state:vt/place:halifax/government</t>
+          <t>ocd-jurisdiction/country:us/state:vt/place:guilford/government</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>http://www.halifaxvermont.com</t>
+          <t>http://www.guilfordschool.org</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -6361,7 +6361,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Hancock</t>
+          <t>Halifax</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -6371,17 +6371,17 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Addison</t>
+          <t>Windham</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>ocd-jurisdiction/country:us/state:vt/place:hancock/government</t>
+          <t>ocd-jurisdiction/country:us/state:vt/place:halifax/government</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Needs Research</t>
+          <t>http://www.halifaxvermont.com</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -6408,7 +6408,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Hardwick</t>
+          <t>Hancock</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -6418,17 +6418,17 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Caledonia</t>
+          <t>Addison</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>ocd-jurisdiction/country:us/state:vt/place:hardwick/government</t>
+          <t>ocd-jurisdiction/country:us/state:vt/place:hancock/government</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>http://www.nek4u.net/</t>
+          <t>Needs Research</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -6455,7 +6455,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Hartford</t>
+          <t>Hardwick</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -6465,17 +6465,17 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Windsor</t>
+          <t>Caledonia</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>ocd-jurisdiction/country:us/state:vt/place:hartford/government</t>
+          <t>ocd-jurisdiction/country:us/state:vt/place:hardwick/government</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>http://www.hartfordvt.org</t>
+          <t>http://www.nek4u.net/</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -6502,7 +6502,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Hartland</t>
+          <t>Hartford</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -6517,12 +6517,12 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>ocd-jurisdiction/country:us/state:vt/place:hartland/government</t>
+          <t>ocd-jurisdiction/country:us/state:vt/place:hartford/government</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>http://www.hartland.govoffice.com</t>
+          <t>http://www.hartfordvt.org</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -6549,7 +6549,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Highgate</t>
+          <t>Hartland</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -6559,17 +6559,17 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Franklin</t>
+          <t>Windsor</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>ocd-jurisdiction/country:us/state:vt/place:highgate/government</t>
+          <t>ocd-jurisdiction/country:us/state:vt/place:hartland/government</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>http://www.virtualvermont.com/towns/highgate.html</t>
+          <t>http://www.hartland.govoffice.com</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -6596,7 +6596,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Hinesburg</t>
+          <t>Highgate</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -6606,17 +6606,17 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Chittenden</t>
+          <t>Franklin</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>ocd-jurisdiction/country:us/state:vt/place:hinesburg/government</t>
+          <t>ocd-jurisdiction/country:us/state:vt/place:highgate/government</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>http://www.hinesburg.org/</t>
+          <t>http://www.virtualvermont.com/towns/highgate.html</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -6643,7 +6643,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Holland</t>
+          <t>Hinesburg</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -6653,17 +6653,17 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Orleans</t>
+          <t>Chittenden</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>ocd-jurisdiction/country:us/state:vt/place:holland/government</t>
+          <t>ocd-jurisdiction/country:us/state:vt/place:hinesburg/government</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>http://www.hollanddvt.us</t>
+          <t>http://www.hinesburg.org/</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -6690,7 +6690,7 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Hubbardton</t>
+          <t>Holland</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -6700,17 +6700,17 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Rutland</t>
+          <t>Orleans</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>ocd-jurisdiction/country:us/state:vt/place:hubbardton/government</t>
+          <t>ocd-jurisdiction/country:us/state:vt/place:holland/government</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Needs Research</t>
+          <t>http://www.hollanddvt.us</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -6737,7 +6737,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Huntington</t>
+          <t>Hubbardton</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -6747,17 +6747,17 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Chittenden</t>
+          <t>Rutland</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>ocd-jurisdiction/country:us/state:vt/place:huntington/government</t>
+          <t>ocd-jurisdiction/country:us/state:vt/place:hubbardton/government</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>http://www.huntingtonvt.org</t>
+          <t>Needs Research</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -6784,7 +6784,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Hyde Park</t>
+          <t>Huntington</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -6794,17 +6794,17 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Lamoille</t>
+          <t>Chittenden</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>ocd-jurisdiction/country:us/state:vt/place:hyde-park-35050/government</t>
+          <t>ocd-jurisdiction/country:us/state:vt/place:huntington/government</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>http://www.hydeparkvt.com</t>
+          <t>http://www.huntingtonvt.org</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -6836,7 +6836,7 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Village</t>
+          <t>Town</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -6846,7 +6846,7 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>ocd-jurisdiction/country:us/state:vt/place:hyde-park/government</t>
+          <t>ocd-jurisdiction/country:us/state:vt/place:hyde-park-35050/government</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
@@ -6878,27 +6878,27 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Ira</t>
+          <t>Hyde Park</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Town</t>
+          <t>Village</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Rutland</t>
+          <t>Lamoille</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>ocd-jurisdiction/country:us/state:vt/place:ira/government</t>
+          <t>ocd-jurisdiction/country:us/state:vt/place:hyde-park/government</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Needs Research</t>
+          <t>http://www.hydeparkvt.com</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -6925,7 +6925,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Irasburg</t>
+          <t>Ira</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -6935,17 +6935,17 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Orleans</t>
+          <t>Rutland</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>ocd-jurisdiction/country:us/state:vt/place:irasburg/government</t>
+          <t>ocd-jurisdiction/country:us/state:vt/place:ira/government</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>http://www.irasburgvt.com</t>
+          <t>Needs Research</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -6972,7 +6972,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Isle La Motte</t>
+          <t>Irasburg</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -6982,17 +6982,17 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Grand Isle</t>
+          <t>Orleans</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>ocd-jurisdiction/country:us/state:vt/place:isle-la-motte/government</t>
+          <t>ocd-jurisdiction/country:us/state:vt/place:irasburg/government</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Needs Research</t>
+          <t>http://www.irasburgvt.com</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -7019,22 +7019,22 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Jacksonville</t>
+          <t>Isle La Motte</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Village</t>
+          <t>Town</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Windham</t>
+          <t>Grand Isle</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>ocd-jurisdiction/country:us/state:vt/place:jacksonville/government</t>
+          <t>ocd-jurisdiction/country:us/state:vt/place:isle-la-motte/government</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
@@ -7066,12 +7066,12 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Jamaica</t>
+          <t>Jacksonville</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Town</t>
+          <t>Village</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -7081,12 +7081,12 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>ocd-jurisdiction/country:us/state:vt/place:jamaica/government</t>
+          <t>ocd-jurisdiction/country:us/state:vt/place:jacksonville/government</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>http://www.jamaicavermont.org</t>
+          <t>Needs Research</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -7113,7 +7113,7 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Jay</t>
+          <t>Jamaica</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -7123,17 +7123,17 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Orleans</t>
+          <t>Windham</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>ocd-jurisdiction/country:us/state:vt/place:jay/government</t>
+          <t>ocd-jurisdiction/country:us/state:vt/place:jamaica/government</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Needs Research</t>
+          <t>http://www.jamaicavermont.org</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -7160,22 +7160,22 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Jeffersonville</t>
+          <t>Jay</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Village</t>
+          <t>Town</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Lamoille</t>
+          <t>Orleans</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>ocd-jurisdiction/country:us/state:vt/place:jeffersonville/government</t>
+          <t>ocd-jurisdiction/country:us/state:vt/place:jay/government</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
@@ -7207,27 +7207,27 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Jericho</t>
+          <t>Jeffersonville</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Town</t>
+          <t>Village</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Chittenden</t>
+          <t>Lamoille</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>ocd-jurisdiction/country:us/state:vt/place:jericho/government</t>
+          <t>ocd-jurisdiction/country:us/state:vt/place:jeffersonville/government</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>http://www.jerichovt.gov/</t>
+          <t>Needs Research</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -7254,7 +7254,7 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Johnson</t>
+          <t>Jericho</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -7264,17 +7264,17 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Lamoille</t>
+          <t>Chittenden</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>ocd-jurisdiction/country:us/state:vt/place:johnson-37075/government</t>
+          <t>ocd-jurisdiction/country:us/state:vt/place:jericho/government</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>http://townofjohnson.com/</t>
+          <t>http://www.jerichovt.gov/</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -7301,7 +7301,7 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Johnson</t>
+          <t>Jericho</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -7311,17 +7311,17 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Lamoille</t>
+          <t>Chittenden</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>ocd-jurisdiction/country:us/state:vt/place:johnson/government</t>
+          <t>ocd-jurisdiction/country:us/state:vt/place:jericho-village/government</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>http://www.townofjohnson.com</t>
+          <t>Needs Research</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -7341,14 +7341,14 @@
       </c>
       <c r="J116" t="inlineStr">
         <is>
-          <t>Seeded from repo jurisdiction file (Census 2022 Census of Governments). Charter chapter in Title 24 Appendix V.S.A. and code link to be backfilled from the Vermont Legislature municipal charters index and the official municipal website.</t>
+          <t>Added 2026-10-16 (issue #163 fix): missing from the Census 2022 seed; verified on the Vermont Secretary of State (VSARA) List of Incorporated Villages. Charter/code/website backfill as per sheet.</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Killington</t>
+          <t>Johnson</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -7358,17 +7358,17 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Rutland</t>
+          <t>Lamoille</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>ocd-jurisdiction/country:us/state:vt/place:killington/government</t>
+          <t>ocd-jurisdiction/country:us/state:vt/place:johnson-37075/government</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>http://www.killingtontown.com/</t>
+          <t>http://townofjohnson.com/</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -7395,27 +7395,27 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Kirby</t>
+          <t>Johnson</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Town</t>
+          <t>Village</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Caledonia</t>
+          <t>Lamoille</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>ocd-jurisdiction/country:us/state:vt/place:kirby/government</t>
+          <t>ocd-jurisdiction/country:us/state:vt/place:johnson/government</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Needs Research</t>
+          <t>http://www.townofjohnson.com</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
@@ -7442,7 +7442,7 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Landgrove</t>
+          <t>Killington</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -7452,17 +7452,17 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Bennington</t>
+          <t>Rutland</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>ocd-jurisdiction/country:us/state:vt/place:landgrove/government</t>
+          <t>ocd-jurisdiction/country:us/state:vt/place:killington/government</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Needs Research</t>
+          <t>http://www.killingtontown.com/</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -7489,7 +7489,7 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Leicester</t>
+          <t>Kirby</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -7499,12 +7499,12 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Addison</t>
+          <t>Caledonia</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>ocd-jurisdiction/country:us/state:vt/place:leicester/government</t>
+          <t>ocd-jurisdiction/country:us/state:vt/place:kirby/government</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
@@ -7536,7 +7536,7 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Lemington</t>
+          <t>Landgrove</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -7546,12 +7546,12 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Essex</t>
+          <t>Bennington</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>ocd-jurisdiction/country:us/state:vt/place:lemington/government</t>
+          <t>ocd-jurisdiction/country:us/state:vt/place:landgrove/government</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
@@ -7583,7 +7583,7 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Lincoln</t>
+          <t>Leicester</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -7598,12 +7598,12 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>ocd-jurisdiction/country:us/state:vt/place:lincoln/government</t>
+          <t>ocd-jurisdiction/country:us/state:vt/place:leicester/government</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>http://www.lincolnvermont.org</t>
+          <t>Needs Research</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
@@ -7630,7 +7630,7 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Londonderry</t>
+          <t>Lemington</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -7640,12 +7640,12 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Windham</t>
+          <t>Essex</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>ocd-jurisdiction/country:us/state:vt/place:londonderry/government</t>
+          <t>ocd-jurisdiction/country:us/state:vt/place:lemington/government</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
@@ -7677,7 +7677,7 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Lowell</t>
+          <t>Lincoln</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -7687,17 +7687,17 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Orleans</t>
+          <t>Addison</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>ocd-jurisdiction/country:us/state:vt/place:lowell/government</t>
+          <t>ocd-jurisdiction/country:us/state:vt/place:lincoln/government</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Needs Research</t>
+          <t>http://www.lincolnvermont.org</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
@@ -7724,7 +7724,7 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Ludlow</t>
+          <t>Londonderry</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -7734,17 +7734,17 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Windsor</t>
+          <t>Windham</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>ocd-jurisdiction/country:us/state:vt/place:ludlow-41275/government</t>
+          <t>ocd-jurisdiction/country:us/state:vt/place:londonderry/government</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>http://www.ludlow.vt.us</t>
+          <t>Needs Research</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
@@ -7771,27 +7771,27 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Ludlow</t>
+          <t>Lowell</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Village</t>
+          <t>Town</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Windsor</t>
+          <t>Orleans</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>ocd-jurisdiction/country:us/state:vt/place:ludlow/government</t>
+          <t>ocd-jurisdiction/country:us/state:vt/place:lowell/government</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>http://www.ludlow.vt.us</t>
+          <t>Needs Research</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
@@ -7818,7 +7818,7 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Lunenburg</t>
+          <t>Ludlow</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -7828,17 +7828,17 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Essex</t>
+          <t>Windsor</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>ocd-jurisdiction/country:us/state:vt/place:lunenburg/government</t>
+          <t>ocd-jurisdiction/country:us/state:vt/place:ludlow-41275/government</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Needs Research</t>
+          <t>http://www.ludlow.vt.us</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
@@ -7865,27 +7865,27 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Lyndon</t>
+          <t>Ludlow</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Town</t>
+          <t>Village</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Caledonia</t>
+          <t>Windsor</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>ocd-jurisdiction/country:us/state:vt/place:lyndon/government</t>
+          <t>ocd-jurisdiction/country:us/state:vt/place:ludlow/government</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>http://www.lyndonvt.org</t>
+          <t>http://www.ludlow.vt.us</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
@@ -7912,27 +7912,27 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Lyndonville</t>
+          <t>Lunenburg</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Village</t>
+          <t>Town</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Caledonia</t>
+          <t>Essex</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>ocd-jurisdiction/country:us/state:vt/place:lyndonville/government</t>
+          <t>ocd-jurisdiction/country:us/state:vt/place:lunenburg/government</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>http://www.lyndonville.us</t>
+          <t>Needs Research</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
@@ -7959,7 +7959,7 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Maidstone</t>
+          <t>Lyndon</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -7969,17 +7969,17 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Essex</t>
+          <t>Caledonia</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>ocd-jurisdiction/country:us/state:vt/place:maidstone/government</t>
+          <t>ocd-jurisdiction/country:us/state:vt/place:lyndon/government</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Needs Research</t>
+          <t>http://www.lyndonvt.org</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
@@ -8006,7 +8006,7 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Manchester</t>
+          <t>Maidstone</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -8016,17 +8016,17 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Bennington</t>
+          <t>Essex</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>ocd-jurisdiction/country:us/state:vt/place:manchester-42850/government</t>
+          <t>ocd-jurisdiction/country:us/state:vt/place:maidstone/government</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>http://www.manchester-vt.gov/</t>
+          <t>Needs Research</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
@@ -8058,7 +8058,7 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Village</t>
+          <t>Town</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -8068,12 +8068,12 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>ocd-jurisdiction/country:us/state:vt/place:manchester/government</t>
+          <t>ocd-jurisdiction/country:us/state:vt/place:manchester-42850/government</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>http://www.villageofmanchester.com</t>
+          <t>http://www.manchester-vt.gov/</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
@@ -8100,27 +8100,27 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Marlboro</t>
+          <t>Manchester</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Town</t>
+          <t>Village</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Windham</t>
+          <t>Bennington</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>ocd-jurisdiction/country:us/state:vt/place:marlboro/government</t>
+          <t>ocd-jurisdiction/country:us/state:vt/place:manchester/government</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>http://www.marlboro.vt.us</t>
+          <t>http://www.villageofmanchester.com</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
@@ -8147,7 +8147,7 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Marshfield</t>
+          <t>Marlboro</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -8157,17 +8157,17 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Washington</t>
+          <t>Windham</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>ocd-jurisdiction/country:us/state:vt/place:marshfield-43600/government</t>
+          <t>ocd-jurisdiction/country:us/state:vt/place:marlboro/government</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>http://www.town.marshfield.vt.us</t>
+          <t>http://www.marlboro.vt.us</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
@@ -8199,7 +8199,7 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Village</t>
+          <t>Town</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
@@ -8209,12 +8209,12 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>ocd-jurisdiction/country:us/state:vt/place:marshfield/government</t>
+          <t>ocd-jurisdiction/country:us/state:vt/place:marshfield-43600/government</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Needs Research</t>
+          <t>http://www.town.marshfield.vt.us</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
@@ -8241,27 +8241,27 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Mendon</t>
+          <t>Marshfield</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Town</t>
+          <t>Village</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Rutland</t>
+          <t>Washington</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>ocd-jurisdiction/country:us/state:vt/place:mendon/government</t>
+          <t>ocd-jurisdiction/country:us/state:vt/place:marshfield/government</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>http://www.mendonvt.org/</t>
+          <t>Needs Research</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
@@ -8288,7 +8288,7 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Middlebury</t>
+          <t>Mendon</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -8298,17 +8298,17 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Addison</t>
+          <t>Rutland</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>ocd-jurisdiction/country:us/state:vt/place:middlebury/government</t>
+          <t>ocd-jurisdiction/country:us/state:vt/place:mendon/government</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>http://www.middlebury.govoffice.com/</t>
+          <t>http://www.mendonvt.org/</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
@@ -8335,7 +8335,7 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Middlesex</t>
+          <t>Middlebury</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -8345,17 +8345,17 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Washington</t>
+          <t>Addison</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>ocd-jurisdiction/country:us/state:vt/place:middlesex/government</t>
+          <t>ocd-jurisdiction/country:us/state:vt/place:middlebury/government</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>http://www.middlesexvt.org</t>
+          <t>http://www.middlebury.govoffice.com/</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
@@ -8382,7 +8382,7 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Middletown Springs</t>
+          <t>Middlesex</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -8392,17 +8392,17 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Rutland</t>
+          <t>Washington</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>ocd-jurisdiction/country:us/state:vt/place:middletown-springs/government</t>
+          <t>ocd-jurisdiction/country:us/state:vt/place:middlesex/government</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Needs Research</t>
+          <t>http://www.middlesexvt.org</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
@@ -8429,7 +8429,7 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Milton</t>
+          <t>Middletown Springs</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -8439,17 +8439,17 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Chittenden</t>
+          <t>Rutland</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>ocd-jurisdiction/country:us/state:vt/place:milton/government</t>
+          <t>ocd-jurisdiction/country:us/state:vt/place:middletown-springs/government</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>http://www.milton.govoffice2.com</t>
+          <t>Needs Research</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
@@ -8476,7 +8476,7 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Monkton</t>
+          <t>Milton</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -8486,17 +8486,17 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Addison</t>
+          <t>Chittenden</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>ocd-jurisdiction/country:us/state:vt/place:monkton/government</t>
+          <t>ocd-jurisdiction/country:us/state:vt/place:milton/government</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>http://www.monktonvt.com</t>
+          <t>http://www.milton.govoffice2.com</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
@@ -8523,7 +8523,7 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Montgomery</t>
+          <t>Monkton</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -8533,17 +8533,17 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Franklin</t>
+          <t>Addison</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>ocd-jurisdiction/country:us/state:vt/place:montgomery/government</t>
+          <t>ocd-jurisdiction/country:us/state:vt/place:monkton/government</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>http://www.montgomeryvt.us</t>
+          <t>http://www.monktonvt.com</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
@@ -8570,27 +8570,27 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Montpelier</t>
+          <t>Montgomery</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>City</t>
+          <t>Town</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Washington</t>
+          <t>Franklin</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>ocd-jurisdiction/country:us/state:vt/place:montpelier/government</t>
+          <t>ocd-jurisdiction/country:us/state:vt/place:montgomery/government</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>http://www.montpelier-vt.org/</t>
+          <t>http://www.montgomeryvt.us</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
@@ -8617,12 +8617,12 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Moretown</t>
+          <t>Montpelier</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Town</t>
+          <t>City</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
@@ -8632,12 +8632,12 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>ocd-jurisdiction/country:us/state:vt/place:moretown/government</t>
+          <t>ocd-jurisdiction/country:us/state:vt/place:montpelier/government</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>http://www.moretownvt.org</t>
+          <t>http://www.montpelier-vt.org/</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
@@ -8664,7 +8664,7 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Morgan</t>
+          <t>Moretown</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -8674,17 +8674,17 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Orleans</t>
+          <t>Washington</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>ocd-jurisdiction/country:us/state:vt/place:morgan/government</t>
+          <t>ocd-jurisdiction/country:us/state:vt/place:moretown/government</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>http://www.townofmorgan.com</t>
+          <t>http://www.moretownvt.org</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
@@ -8711,7 +8711,7 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Morristown</t>
+          <t>Morgan</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -8721,17 +8721,17 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Lamoille</t>
+          <t>Orleans</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>ocd-jurisdiction/country:us/state:vt/place:morristown/government</t>
+          <t>ocd-jurisdiction/country:us/state:vt/place:morgan/government</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>http://www.morristownvt.org/home.html</t>
+          <t>http://www.townofmorgan.com</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
@@ -8758,12 +8758,12 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Morrisville</t>
+          <t>Morristown</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Village</t>
+          <t>Town</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
@@ -8773,12 +8773,12 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>ocd-jurisdiction/country:us/state:vt/place:morrisville/government</t>
+          <t>ocd-jurisdiction/country:us/state:vt/place:morristown/government</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Needs Research</t>
+          <t>http://www.morristownvt.org/home.html</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
@@ -8805,22 +8805,22 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Mount Holly</t>
+          <t>Morrisville</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Town</t>
+          <t>Village</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Rutland</t>
+          <t>Lamoille</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>ocd-jurisdiction/country:us/state:vt/place:mount-holly/government</t>
+          <t>ocd-jurisdiction/country:us/state:vt/place:morrisville/government</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
@@ -8852,7 +8852,7 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>Mount Tabor</t>
+          <t>Mount Holly</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -8867,7 +8867,7 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>ocd-jurisdiction/country:us/state:vt/place:mount-tabor/government</t>
+          <t>ocd-jurisdiction/country:us/state:vt/place:mount-holly/government</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
@@ -8899,7 +8899,7 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>New Haven</t>
+          <t>Mount Tabor</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -8909,12 +8909,12 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Addison</t>
+          <t>Rutland</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>ocd-jurisdiction/country:us/state:vt/place:new-haven/government</t>
+          <t>ocd-jurisdiction/country:us/state:vt/place:mount-tabor/government</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
@@ -8946,7 +8946,7 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>Newark</t>
+          <t>New Haven</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -8956,12 +8956,12 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Caledonia</t>
+          <t>Addison</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>ocd-jurisdiction/country:us/state:vt/place:newark/government</t>
+          <t>ocd-jurisdiction/country:us/state:vt/place:new-haven/government</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
@@ -8993,7 +8993,7 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>Newbury</t>
+          <t>Newark</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -9003,12 +9003,12 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Orange</t>
+          <t>Caledonia</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>ocd-jurisdiction/country:us/state:vt/place:newbury-48175/government</t>
+          <t>ocd-jurisdiction/country:us/state:vt/place:newark/government</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
@@ -9045,7 +9045,7 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Village</t>
+          <t>Town</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
@@ -9055,7 +9055,7 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>ocd-jurisdiction/country:us/state:vt/place:newbury/government</t>
+          <t>ocd-jurisdiction/country:us/state:vt/place:newbury-48175/government</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
@@ -9087,27 +9087,27 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>Newfane</t>
+          <t>Newbury</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Town</t>
+          <t>Village</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Windham</t>
+          <t>Orange</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>ocd-jurisdiction/country:us/state:vt/place:newfane-48400/government</t>
+          <t>ocd-jurisdiction/country:us/state:vt/place:newbury/government</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>http://www.newfanevt.com</t>
+          <t>Needs Research</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
@@ -9139,7 +9139,7 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Village</t>
+          <t>Town</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
@@ -9149,12 +9149,12 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>ocd-jurisdiction/country:us/state:vt/place:newfane/government</t>
+          <t>ocd-jurisdiction/country:us/state:vt/place:newfane-48400/government</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Needs Research</t>
+          <t>http://www.newfanevt.com</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
@@ -9181,22 +9181,22 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>Newport</t>
+          <t>Newfane</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Town</t>
+          <t>Village</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Orleans</t>
+          <t>Windham</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>ocd-jurisdiction/country:us/state:vt/place:newport-48925/government</t>
+          <t>ocd-jurisdiction/country:us/state:vt/place:newfane/government</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
@@ -9233,7 +9233,7 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>City</t>
+          <t>Town</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
@@ -9243,12 +9243,12 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>ocd-jurisdiction/country:us/state:vt/place:newport/government</t>
+          <t>ocd-jurisdiction/country:us/state:vt/place:newport-48925/government</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>http://www.newportvermont.org/</t>
+          <t>Needs Research</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
@@ -9275,27 +9275,27 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>North Bennington</t>
+          <t>Newport</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Village</t>
+          <t>City</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Bennington</t>
+          <t>Orleans</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>ocd-jurisdiction/country:us/state:vt/place:north-bennington/government</t>
+          <t>ocd-jurisdiction/country:us/state:vt/place:newport/government</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>http://www.northbennington.org</t>
+          <t>http://www.newportvermont.org/</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
@@ -9322,27 +9322,27 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>North Hero</t>
+          <t>North Bennington</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Town</t>
+          <t>Village</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Grand Isle</t>
+          <t>Bennington</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>ocd-jurisdiction/country:us/state:vt/place:north-hero/government</t>
+          <t>ocd-jurisdiction/country:us/state:vt/place:north-bennington/government</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>http://www.northherovt.com</t>
+          <t>http://www.northbennington.org</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
@@ -9369,27 +9369,27 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>North Troy</t>
+          <t>North Hero</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Village</t>
+          <t>Town</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Orleans</t>
+          <t>Grand Isle</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>ocd-jurisdiction/country:us/state:vt/place:north-troy/government</t>
+          <t>ocd-jurisdiction/country:us/state:vt/place:north-hero/government</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Needs Research</t>
+          <t>http://www.northherovt.com</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
@@ -9416,27 +9416,27 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>Northfield</t>
+          <t>North Troy</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Town</t>
+          <t>Village</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Washington</t>
+          <t>Orleans</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>ocd-jurisdiction/country:us/state:vt/place:northfield/government</t>
+          <t>ocd-jurisdiction/country:us/state:vt/place:north-troy/government</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>http://www.northfield-vt.gov/</t>
+          <t>Needs Research</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
@@ -9463,7 +9463,7 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>Norton</t>
+          <t>Northfield</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -9473,17 +9473,17 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Essex</t>
+          <t>Washington</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>ocd-jurisdiction/country:us/state:vt/place:norton/government</t>
+          <t>ocd-jurisdiction/country:us/state:vt/place:northfield/government</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Needs Research</t>
+          <t>http://www.northfield-vt.gov/</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
@@ -9510,7 +9510,7 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>Norwich</t>
+          <t>Norton</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -9520,17 +9520,17 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Windsor</t>
+          <t>Essex</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>ocd-jurisdiction/country:us/state:vt/place:norwich/government</t>
+          <t>ocd-jurisdiction/country:us/state:vt/place:norton/government</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>www.norwich.vt.us</t>
+          <t>Needs Research</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
@@ -9557,27 +9557,27 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>Old Bennington</t>
+          <t>Norwich</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Village</t>
+          <t>Town</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Bennington</t>
+          <t>Windsor</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>ocd-jurisdiction/country:us/state:vt/place:old-bennington/government</t>
+          <t>ocd-jurisdiction/country:us/state:vt/place:norwich/government</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Needs Research</t>
+          <t>www.norwich.vt.us</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
@@ -9604,27 +9604,27 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>Orange</t>
+          <t>Old Bennington</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Town</t>
+          <t>Village</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Orange</t>
+          <t>Bennington</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>ocd-jurisdiction/country:us/state:vt/place:orange/government</t>
+          <t>ocd-jurisdiction/country:us/state:vt/place:old-bennington/government</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>http://www.orangevt.org</t>
+          <t>Needs Research</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
@@ -9651,27 +9651,27 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>Orleans</t>
+          <t>Orange</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Village</t>
+          <t>Town</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Orleans</t>
+          <t>Orange</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>ocd-jurisdiction/country:us/state:vt/place:orleans/government</t>
+          <t>ocd-jurisdiction/country:us/state:vt/place:orange/government</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Needs Research</t>
+          <t>http://www.orangevt.org</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
@@ -9698,27 +9698,27 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>Orwell</t>
+          <t>Orleans</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Town</t>
+          <t>Village</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Addison</t>
+          <t>Orleans</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>ocd-jurisdiction/country:us/state:vt/place:orwell/government</t>
+          <t>ocd-jurisdiction/country:us/state:vt/place:orleans/government</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>http://www.town-of-orwell.org</t>
+          <t>Needs Research</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
@@ -9745,7 +9745,7 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>Panton</t>
+          <t>Orwell</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -9760,12 +9760,12 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>ocd-jurisdiction/country:us/state:vt/place:panton/government</t>
+          <t>ocd-jurisdiction/country:us/state:vt/place:orwell/government</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>http://www.pantonvt.us</t>
+          <t>http://www.town-of-orwell.org</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
@@ -9792,7 +9792,7 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>Pawlet</t>
+          <t>Panton</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -9802,17 +9802,17 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Rutland</t>
+          <t>Addison</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>ocd-jurisdiction/country:us/state:vt/place:pawlet/government</t>
+          <t>ocd-jurisdiction/country:us/state:vt/place:panton/government</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Needs Research</t>
+          <t>http://www.pantonvt.us</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
@@ -9839,7 +9839,7 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>Peacham</t>
+          <t>Pawlet</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -9849,17 +9849,17 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Caledonia</t>
+          <t>Rutland</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>ocd-jurisdiction/country:us/state:vt/place:peacham/government</t>
+          <t>ocd-jurisdiction/country:us/state:vt/place:pawlet/government</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>http://www.peacham.net</t>
+          <t>Needs Research</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
@@ -9886,7 +9886,7 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>Peru</t>
+          <t>Peacham</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -9896,17 +9896,17 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Bennington</t>
+          <t>Caledonia</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>ocd-jurisdiction/country:us/state:vt/place:peru/government</t>
+          <t>ocd-jurisdiction/country:us/state:vt/place:peacham/government</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Needs Research</t>
+          <t>http://www.peacham.net</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
@@ -9933,7 +9933,7 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>Pittsfield</t>
+          <t>Peru</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -9943,17 +9943,17 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Rutland</t>
+          <t>Bennington</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>ocd-jurisdiction/country:us/state:vt/place:pittsfield/government</t>
+          <t>ocd-jurisdiction/country:us/state:vt/place:peru/government</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>http://www.pittsfieldvt.org</t>
+          <t>Needs Research</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
@@ -9980,7 +9980,7 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>Pittsford</t>
+          <t>Pittsfield</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -9995,12 +9995,12 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>ocd-jurisdiction/country:us/state:vt/place:pittsford/government</t>
+          <t>ocd-jurisdiction/country:us/state:vt/place:pittsfield/government</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>http://www.pittsfordvermont.com</t>
+          <t>http://www.pittsfieldvt.org</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
@@ -10027,7 +10027,7 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>Plainfield</t>
+          <t>Pittsford</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -10037,17 +10037,17 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Washington</t>
+          <t>Rutland</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>ocd-jurisdiction/country:us/state:vt/place:plainfield/government</t>
+          <t>ocd-jurisdiction/country:us/state:vt/place:pittsford/government</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>Needs Research</t>
+          <t>http://www.pittsfordvermont.com</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
@@ -10074,7 +10074,7 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>Plymouth</t>
+          <t>Plainfield</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -10084,12 +10084,12 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Windsor</t>
+          <t>Washington</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>ocd-jurisdiction/country:us/state:vt/place:plymouth/government</t>
+          <t>ocd-jurisdiction/country:us/state:vt/place:plainfield/government</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
@@ -10121,7 +10121,7 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>Pomfret</t>
+          <t>Plymouth</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -10136,12 +10136,12 @@
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>ocd-jurisdiction/country:us/state:vt/place:pomfret/government</t>
+          <t>ocd-jurisdiction/country:us/state:vt/place:plymouth/government</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>http://www.pomfretvt.us</t>
+          <t>Needs Research</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
@@ -10168,7 +10168,7 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>Poultney</t>
+          <t>Pomfret</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -10178,17 +10178,17 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Rutland</t>
+          <t>Windsor</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>ocd-jurisdiction/country:us/state:vt/place:poultney-56875/government</t>
+          <t>ocd-jurisdiction/country:us/state:vt/place:pomfret/government</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>http://www.poultneyvt.com/chamber-of-commerce/town-government-directory/</t>
+          <t>http://www.pomfretvt.us</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
@@ -10220,7 +10220,7 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Village</t>
+          <t>Town</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
@@ -10230,12 +10230,12 @@
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>ocd-jurisdiction/country:us/state:vt/place:poultney/government</t>
+          <t>ocd-jurisdiction/country:us/state:vt/place:poultney-56875/government</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>Needs Research</t>
+          <t>http://www.poultneyvt.com/chamber-of-commerce/town-government-directory/</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
@@ -10262,22 +10262,22 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>Pownal</t>
+          <t>Poultney</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Town</t>
+          <t>Village</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Bennington</t>
+          <t>Rutland</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>ocd-jurisdiction/country:us/state:vt/place:pownal/government</t>
+          <t>ocd-jurisdiction/country:us/state:vt/place:poultney/government</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
@@ -10309,7 +10309,7 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>Proctor</t>
+          <t>Pownal</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -10319,12 +10319,12 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Rutland</t>
+          <t>Bennington</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>ocd-jurisdiction/country:us/state:vt/place:proctor/government</t>
+          <t>ocd-jurisdiction/country:us/state:vt/place:pownal/government</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
@@ -10356,7 +10356,7 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>Putney</t>
+          <t>Proctor</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -10366,17 +10366,17 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Windham</t>
+          <t>Rutland</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>ocd-jurisdiction/country:us/state:vt/place:putney/government</t>
+          <t>ocd-jurisdiction/country:us/state:vt/place:proctor/government</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>http://www.putneyvt.org</t>
+          <t>Needs Research</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
@@ -10403,7 +10403,7 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>Randolph</t>
+          <t>Putney</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -10413,17 +10413,17 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Orange</t>
+          <t>Windham</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>ocd-jurisdiction/country:us/state:vt/place:randolph/government</t>
+          <t>ocd-jurisdiction/country:us/state:vt/place:putney/government</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>http://randolphvt.govoffice2.com/</t>
+          <t>http://www.putneyvt.org</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
@@ -10450,7 +10450,7 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Randolph</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -10460,17 +10460,17 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Windsor</t>
+          <t>Orange</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>ocd-jurisdiction/country:us/state:vt/place:reading/government</t>
+          <t>ocd-jurisdiction/country:us/state:vt/place:randolph/government</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>Needs Research</t>
+          <t>http://randolphvt.govoffice2.com/</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
@@ -10497,7 +10497,7 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>Readsboro</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -10507,17 +10507,17 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Bennington</t>
+          <t>Windsor</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>ocd-jurisdiction/country:us/state:vt/place:readsboro/government</t>
+          <t>ocd-jurisdiction/country:us/state:vt/place:reading/government</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>http://www.officialtownofreadsboro.org</t>
+          <t>Needs Research</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
@@ -10544,7 +10544,7 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>Richford</t>
+          <t>Readsboro</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -10554,17 +10554,17 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Franklin</t>
+          <t>Bennington</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>ocd-jurisdiction/country:us/state:vt/place:richford/government</t>
+          <t>ocd-jurisdiction/country:us/state:vt/place:readsboro/government</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>Needs Research</t>
+          <t>http://www.officialtownofreadsboro.org</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
@@ -10591,7 +10591,7 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>Richmond</t>
+          <t>Richford</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -10601,17 +10601,17 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Chittenden</t>
+          <t>Franklin</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>ocd-jurisdiction/country:us/state:vt/place:richmond/government</t>
+          <t>ocd-jurisdiction/country:us/state:vt/place:richford/government</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>http://www.richmondvt.com</t>
+          <t>Needs Research</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
@@ -10638,7 +10638,7 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>Ripton</t>
+          <t>Richmond</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -10648,17 +10648,17 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Addison</t>
+          <t>Chittenden</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>ocd-jurisdiction/country:us/state:vt/place:ripton/government</t>
+          <t>ocd-jurisdiction/country:us/state:vt/place:richmond/government</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>http://www.riptonvt.org</t>
+          <t>http://www.richmondvt.com</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
@@ -10685,7 +10685,7 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>Rochester</t>
+          <t>Ripton</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -10695,17 +10695,17 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Windsor</t>
+          <t>Addison</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>ocd-jurisdiction/country:us/state:vt/place:rochester/government</t>
+          <t>ocd-jurisdiction/country:us/state:vt/place:ripton/government</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>http://www.rochestervermont.org</t>
+          <t>http://www.riptonvt.org</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
@@ -10732,7 +10732,7 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>Rockingham</t>
+          <t>Rochester</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -10742,17 +10742,17 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Windham</t>
+          <t>Windsor</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>ocd-jurisdiction/country:us/state:vt/place:rockingham/government</t>
+          <t>ocd-jurisdiction/country:us/state:vt/place:rochester/government</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>http://www.rockbf.org</t>
+          <t>http://www.rochestervermont.org</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
@@ -10779,7 +10779,7 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>Roxbury</t>
+          <t>Rockingham</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -10789,17 +10789,17 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Washington</t>
+          <t>Windham</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>ocd-jurisdiction/country:us/state:vt/place:roxbury/government</t>
+          <t>ocd-jurisdiction/country:us/state:vt/place:rockingham/government</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>http://www.roxbury.govoffice2.com/</t>
+          <t>http://www.rockbf.org</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
@@ -10826,7 +10826,7 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>Royalton</t>
+          <t>Roxbury</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -10836,17 +10836,17 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Windsor</t>
+          <t>Washington</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>ocd-jurisdiction/country:us/state:vt/place:royalton/government</t>
+          <t>ocd-jurisdiction/country:us/state:vt/place:roxbury/government</t>
         </is>
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>Needs Research</t>
+          <t>http://www.roxbury.govoffice2.com/</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
@@ -10873,7 +10873,7 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>Rupert</t>
+          <t>Royalton</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -10883,12 +10883,12 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Bennington</t>
+          <t>Windsor</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>ocd-jurisdiction/country:us/state:vt/place:rupert/government</t>
+          <t>ocd-jurisdiction/country:us/state:vt/place:royalton/government</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
@@ -10920,7 +10920,7 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>Rutland</t>
+          <t>Rupert</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -10930,17 +10930,17 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Rutland</t>
+          <t>Bennington</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>ocd-jurisdiction/country:us/state:vt/place:rutland-61300/government</t>
+          <t>ocd-jurisdiction/country:us/state:vt/place:rupert/government</t>
         </is>
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>http://www.rutlandtown.com/</t>
+          <t>Needs Research</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
@@ -10972,7 +10972,7 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>City</t>
+          <t>Town</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
@@ -10982,12 +10982,12 @@
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>ocd-jurisdiction/country:us/state:vt/place:rutland/government</t>
+          <t>ocd-jurisdiction/country:us/state:vt/place:rutland-61300/government</t>
         </is>
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>http://www.rutlandcity.com</t>
+          <t>http://www.rutlandtown.com/</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
@@ -11014,27 +11014,27 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>Ryegate</t>
+          <t>Rutland</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>Town</t>
+          <t>City</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Caledonia</t>
+          <t>Rutland</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>ocd-jurisdiction/country:us/state:vt/place:ryegate/government</t>
+          <t>ocd-jurisdiction/country:us/state:vt/place:rutland/government</t>
         </is>
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>Needs Research</t>
+          <t>http://www.rutlandcity.com</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
@@ -11061,7 +11061,7 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>Salisbury</t>
+          <t>Ryegate</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -11071,17 +11071,17 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Addison</t>
+          <t>Caledonia</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>ocd-jurisdiction/country:us/state:vt/place:salisbury/government</t>
+          <t>ocd-jurisdiction/country:us/state:vt/place:ryegate/government</t>
         </is>
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>http://www.townofsalisbury.org</t>
+          <t>Needs Research</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
@@ -11108,7 +11108,7 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>Sandgate</t>
+          <t>Salisbury</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -11118,17 +11118,17 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Bennington</t>
+          <t>Addison</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>ocd-jurisdiction/country:us/state:vt/place:sandgate/government</t>
+          <t>ocd-jurisdiction/country:us/state:vt/place:salisbury/government</t>
         </is>
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>http://www.sandgatevermont.org</t>
+          <t>http://www.townofsalisbury.org</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
@@ -11155,27 +11155,27 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>Saxtons River</t>
+          <t>Sandgate</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>Village</t>
+          <t>Town</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Windham</t>
+          <t>Bennington</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>ocd-jurisdiction/country:us/state:vt/place:saxtons-river/government</t>
+          <t>ocd-jurisdiction/country:us/state:vt/place:sandgate/government</t>
         </is>
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>Needs Research</t>
+          <t>http://www.sandgatevermont.org</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
@@ -11202,22 +11202,22 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>Searsburg</t>
+          <t>Saxtons River</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>Town</t>
+          <t>Village</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Bennington</t>
+          <t>Windham</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>ocd-jurisdiction/country:us/state:vt/place:searsburg/government</t>
+          <t>ocd-jurisdiction/country:us/state:vt/place:saxtons-river/government</t>
         </is>
       </c>
       <c r="E199" t="inlineStr">
@@ -11249,7 +11249,7 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>Shaftsbury</t>
+          <t>Searsburg</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -11264,12 +11264,12 @@
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>ocd-jurisdiction/country:us/state:vt/place:shaftsbury/government</t>
+          <t>ocd-jurisdiction/country:us/state:vt/place:searsburg/government</t>
         </is>
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>http://www.shaftsbury.net</t>
+          <t>Needs Research</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
@@ -11296,7 +11296,7 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>Sharon</t>
+          <t>Shaftsbury</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -11306,17 +11306,17 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Windsor</t>
+          <t>Bennington</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>ocd-jurisdiction/country:us/state:vt/place:sharon/government</t>
+          <t>ocd-jurisdiction/country:us/state:vt/place:shaftsbury/government</t>
         </is>
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>Needs Research</t>
+          <t>http://www.shaftsbury.net</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
@@ -11343,7 +11343,7 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>Sheffield</t>
+          <t>Sharon</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -11353,12 +11353,12 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Caledonia</t>
+          <t>Windsor</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>ocd-jurisdiction/country:us/state:vt/place:sheffield/government</t>
+          <t>ocd-jurisdiction/country:us/state:vt/place:sharon/government</t>
         </is>
       </c>
       <c r="E202" t="inlineStr">
@@ -11390,7 +11390,7 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>Shelburne</t>
+          <t>Sheffield</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -11400,17 +11400,17 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Chittenden</t>
+          <t>Caledonia</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>ocd-jurisdiction/country:us/state:vt/place:shelburne/government</t>
+          <t>ocd-jurisdiction/country:us/state:vt/place:sheffield/government</t>
         </is>
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>http://www.shelburnevt.org/departments/79.html</t>
+          <t>Needs Research</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
@@ -11437,7 +11437,7 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>Sheldon</t>
+          <t>Shelburne</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -11447,17 +11447,17 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Franklin</t>
+          <t>Chittenden</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>ocd-jurisdiction/country:us/state:vt/place:sheldon/government</t>
+          <t>ocd-jurisdiction/country:us/state:vt/place:shelburne/government</t>
         </is>
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>Needs Research</t>
+          <t>http://www.shelburnevt.org/departments/79.html</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
@@ -11484,7 +11484,7 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>Shoreham</t>
+          <t>Sheldon</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -11494,12 +11494,12 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Addison</t>
+          <t>Franklin</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>ocd-jurisdiction/country:us/state:vt/place:shoreham/government</t>
+          <t>ocd-jurisdiction/country:us/state:vt/place:sheldon/government</t>
         </is>
       </c>
       <c r="E205" t="inlineStr">
@@ -11531,7 +11531,7 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>Shrewsbury</t>
+          <t>Shoreham</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -11541,17 +11541,17 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Rutland</t>
+          <t>Addison</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>ocd-jurisdiction/country:us/state:vt/place:shrewsbury/government</t>
+          <t>ocd-jurisdiction/country:us/state:vt/place:shoreham/government</t>
         </is>
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>http://www.shrewsburyvt.org</t>
+          <t>Needs Research</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
@@ -11578,27 +11578,27 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>South Burlington</t>
+          <t>Shrewsbury</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>City</t>
+          <t>Town</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Chittenden</t>
+          <t>Rutland</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>ocd-jurisdiction/country:us/state:vt/place:south-burlington/government</t>
+          <t>ocd-jurisdiction/country:us/state:vt/place:shrewsbury/government</t>
         </is>
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>http://www.sburl.com/</t>
+          <t>http://www.shrewsburyvt.org</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
@@ -11625,27 +11625,27 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>South Hero</t>
+          <t>South Burlington</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>Town</t>
+          <t>City</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Grand Isle</t>
+          <t>Chittenden</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>ocd-jurisdiction/country:us/state:vt/place:south-hero/government</t>
+          <t>ocd-jurisdiction/country:us/state:vt/place:south-burlington/government</t>
         </is>
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>Needs Research</t>
+          <t>http://www.sburl.com/</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
@@ -11672,7 +11672,7 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>Springfield</t>
+          <t>South Hero</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -11682,12 +11682,12 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Windsor</t>
+          <t>Grand Isle</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>ocd-jurisdiction/country:us/state:vt/place:springfield/government</t>
+          <t>ocd-jurisdiction/country:us/state:vt/place:south-hero/government</t>
         </is>
       </c>
       <c r="E209" t="inlineStr">
@@ -11719,7 +11719,7 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>St Albans</t>
+          <t>Springfield</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -11729,17 +11729,17 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Franklin</t>
+          <t>Windsor</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>ocd-jurisdiction/country:us/state:vt/place:st-albans-61750/government</t>
+          <t>ocd-jurisdiction/country:us/state:vt/place:springfield/government</t>
         </is>
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>http://www.stalbanstown.com</t>
+          <t>Needs Research</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
@@ -11771,7 +11771,7 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>City</t>
+          <t>Town</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
@@ -11781,12 +11781,12 @@
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>ocd-jurisdiction/country:us/state:vt/place:st-albans/government</t>
+          <t>ocd-jurisdiction/country:us/state:vt/place:st-albans-61750/government</t>
         </is>
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>http://www.stalbansvt.com/</t>
+          <t>http://www.stalbanstown.com</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
@@ -11813,27 +11813,27 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>St George</t>
+          <t>St Albans</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>Town</t>
+          <t>City</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Chittenden</t>
+          <t>Franklin</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>ocd-jurisdiction/country:us/state:vt/place:st-george/government</t>
+          <t>ocd-jurisdiction/country:us/state:vt/place:st-albans/government</t>
         </is>
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>http://www.stgeorgevt.com</t>
+          <t>http://www.stalbansvt.com/</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
@@ -11860,7 +11860,7 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>St Johnsbury</t>
+          <t>St George</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -11870,17 +11870,17 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Caledonia</t>
+          <t>Chittenden</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>ocd-jurisdiction/country:us/state:vt/place:st-johnsbury/government</t>
+          <t>ocd-jurisdiction/country:us/state:vt/place:st-george/government</t>
         </is>
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>http://www.town.stjohnsbury.vt.us</t>
+          <t>http://www.stgeorgevt.com</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
@@ -11907,7 +11907,7 @@
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>Stamford</t>
+          <t>St Johnsbury</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -11917,17 +11917,17 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Bennington</t>
+          <t>Caledonia</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>ocd-jurisdiction/country:us/state:vt/place:stamford/government</t>
+          <t>ocd-jurisdiction/country:us/state:vt/place:st-johnsbury/government</t>
         </is>
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>http://www.stamfordvt.org</t>
+          <t>http://www.town.stjohnsbury.vt.us</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
@@ -11954,7 +11954,7 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>Stannard</t>
+          <t>Stamford</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -11964,17 +11964,17 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Caledonia</t>
+          <t>Bennington</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>ocd-jurisdiction/country:us/state:vt/place:stannard/government</t>
+          <t>ocd-jurisdiction/country:us/state:vt/place:stamford/government</t>
         </is>
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>Needs Research</t>
+          <t>http://www.stamfordvt.org</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
@@ -12001,7 +12001,7 @@
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>Starksboro</t>
+          <t>Stannard</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -12011,17 +12011,17 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Addison</t>
+          <t>Caledonia</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>ocd-jurisdiction/country:us/state:vt/place:starksboro/government</t>
+          <t>ocd-jurisdiction/country:us/state:vt/place:stannard/government</t>
         </is>
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>http://www.starksboro.org</t>
+          <t>Needs Research</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
@@ -12048,7 +12048,7 @@
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>Stockbridge</t>
+          <t>Starksboro</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -12058,17 +12058,17 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Windsor</t>
+          <t>Addison</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>ocd-jurisdiction/country:us/state:vt/place:stockbridge/government</t>
+          <t>ocd-jurisdiction/country:us/state:vt/place:starksboro/government</t>
         </is>
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>Needs Research</t>
+          <t>http://www.starksboro.org</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
@@ -12095,7 +12095,7 @@
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>Stowe</t>
+          <t>Stockbridge</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -12105,17 +12105,17 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Lamoille</t>
+          <t>Windsor</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>ocd-jurisdiction/country:us/state:vt/place:stowe/government</t>
+          <t>ocd-jurisdiction/country:us/state:vt/place:stockbridge/government</t>
         </is>
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>http://www.townofstowevt.org/</t>
+          <t>Needs Research</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
@@ -12142,7 +12142,7 @@
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>Strafford</t>
+          <t>Stowe</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -12152,17 +12152,17 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Orange</t>
+          <t>Lamoille</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>ocd-jurisdiction/country:us/state:vt/place:strafford/government</t>
+          <t>ocd-jurisdiction/country:us/state:vt/place:stowe/government</t>
         </is>
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>http://www.straffordvt.org</t>
+          <t>http://www.townofstowevt.org/</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
@@ -12189,7 +12189,7 @@
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>Stratton</t>
+          <t>Strafford</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -12199,17 +12199,17 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Windham</t>
+          <t>Orange</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>ocd-jurisdiction/country:us/state:vt/place:stratton/government</t>
+          <t>ocd-jurisdiction/country:us/state:vt/place:strafford/government</t>
         </is>
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>http://www.townofstrattonvt.com</t>
+          <t>http://www.straffordvt.org</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
@@ -12236,7 +12236,7 @@
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Stratton</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -12246,17 +12246,17 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Bennington</t>
+          <t>Windham</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>ocd-jurisdiction/country:us/state:vt/place:sunderland/government</t>
+          <t>ocd-jurisdiction/country:us/state:vt/place:stratton/government</t>
         </is>
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>Needs Research</t>
+          <t>http://www.townofstrattonvt.com</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
@@ -12283,7 +12283,7 @@
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>Sutton</t>
+          <t>Sudbury</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -12293,12 +12293,12 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Caledonia</t>
+          <t>Rutland</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>ocd-jurisdiction/country:us/state:vt/place:sutton/government</t>
+          <t>ocd-jurisdiction/country:us/state:vt/place:sudbury/government</t>
         </is>
       </c>
       <c r="E222" t="inlineStr">
@@ -12323,14 +12323,14 @@
       </c>
       <c r="J222" t="inlineStr">
         <is>
-          <t>Seeded from repo jurisdiction file (Census 2022 Census of Governments). Charter chapter in Title 24 Appendix V.S.A. and code link to be backfilled from the Vermont Legislature municipal charters index and the official municipal website.</t>
+          <t>Added 2026-10-16 (issue #163 fix): missing from the Census 2022 seed; verified on the official Vermont.gov Towns &amp; Cities explorer. Charter/code/website backfill as per sheet.</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>Swanton</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -12340,12 +12340,12 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Franklin</t>
+          <t>Bennington</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>ocd-jurisdiction/country:us/state:vt/place:swanton-71725/government</t>
+          <t>ocd-jurisdiction/country:us/state:vt/place:sunderland/government</t>
         </is>
       </c>
       <c r="E223" t="inlineStr">
@@ -12377,27 +12377,27 @@
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>Swanton</t>
+          <t>Sutton</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>Village</t>
+          <t>Town</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Franklin</t>
+          <t>Caledonia</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>ocd-jurisdiction/country:us/state:vt/place:swanton/government</t>
+          <t>ocd-jurisdiction/country:us/state:vt/place:sutton/government</t>
         </is>
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>http://SWANTON.NET</t>
+          <t>Needs Research</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
@@ -12424,7 +12424,7 @@
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>Thetford</t>
+          <t>Swanton</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -12434,17 +12434,17 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Orange</t>
+          <t>Franklin</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>ocd-jurisdiction/country:us/state:vt/place:thetford/government</t>
+          <t>ocd-jurisdiction/country:us/state:vt/place:swanton-71725/government</t>
         </is>
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>http://www.thetfordvermont.us/</t>
+          <t>Needs Research</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
@@ -12471,27 +12471,27 @@
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>Tinmouth</t>
+          <t>Swanton</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>Town</t>
+          <t>Village</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>Rutland</t>
+          <t>Franklin</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>ocd-jurisdiction/country:us/state:vt/place:tinmouth/government</t>
+          <t>ocd-jurisdiction/country:us/state:vt/place:swanton/government</t>
         </is>
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>Needs Research</t>
+          <t>http://SWANTON.NET</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
@@ -12518,7 +12518,7 @@
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>Topsham</t>
+          <t>Thetford</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -12533,12 +12533,12 @@
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>ocd-jurisdiction/country:us/state:vt/place:topsham/government</t>
+          <t>ocd-jurisdiction/country:us/state:vt/place:thetford/government</t>
         </is>
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>Needs Research</t>
+          <t>http://www.thetfordvermont.us/</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
@@ -12565,7 +12565,7 @@
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>Townshend</t>
+          <t>Tinmouth</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -12575,12 +12575,12 @@
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>Windham</t>
+          <t>Rutland</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>ocd-jurisdiction/country:us/state:vt/place:townshend/government</t>
+          <t>ocd-jurisdiction/country:us/state:vt/place:tinmouth/government</t>
         </is>
       </c>
       <c r="E228" t="inlineStr">
@@ -12612,7 +12612,7 @@
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>Troy</t>
+          <t>Topsham</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
@@ -12622,17 +12622,17 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Orleans</t>
+          <t>Orange</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>ocd-jurisdiction/country:us/state:vt/place:troy/government</t>
+          <t>ocd-jurisdiction/country:us/state:vt/place:topsham/government</t>
         </is>
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>www.troyvt.org</t>
+          <t>Needs Research</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
@@ -12659,7 +12659,7 @@
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>Tunbridge</t>
+          <t>Townshend</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
@@ -12669,12 +12669,12 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Orange</t>
+          <t>Windham</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>ocd-jurisdiction/country:us/state:vt/place:tunbridge/government</t>
+          <t>ocd-jurisdiction/country:us/state:vt/place:townshend/government</t>
         </is>
       </c>
       <c r="E230" t="inlineStr">
@@ -12706,7 +12706,7 @@
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>Underhill</t>
+          <t>Troy</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
@@ -12716,17 +12716,17 @@
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>Chittenden</t>
+          <t>Orleans</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>ocd-jurisdiction/country:us/state:vt/place:underhill/government</t>
+          <t>ocd-jurisdiction/country:us/state:vt/place:troy/government</t>
         </is>
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>http://www.underhillvt.gov</t>
+          <t>www.troyvt.org</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
@@ -12753,27 +12753,27 @@
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>Vergennes</t>
+          <t>Tunbridge</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>City</t>
+          <t>Town</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>Addison</t>
+          <t>Orange</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>ocd-jurisdiction/country:us/state:vt/place:vergennes/government</t>
+          <t>ocd-jurisdiction/country:us/state:vt/place:tunbridge/government</t>
         </is>
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>http://www.vergennes.org/</t>
+          <t>Needs Research</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
@@ -12800,7 +12800,7 @@
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>Vernon</t>
+          <t>Underhill</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
@@ -12810,17 +12810,17 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>Windham</t>
+          <t>Chittenden</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>ocd-jurisdiction/country:us/state:vt/place:vernon/government</t>
+          <t>ocd-jurisdiction/country:us/state:vt/place:underhill/government</t>
         </is>
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>Needs Research</t>
+          <t>http://www.underhillvt.gov</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
@@ -12847,27 +12847,27 @@
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>Vershire</t>
+          <t>Vergennes</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>Town</t>
+          <t>City</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>Orange</t>
+          <t>Addison</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>ocd-jurisdiction/country:us/state:vt/place:vershire/government</t>
+          <t>ocd-jurisdiction/country:us/state:vt/place:vergennes/government</t>
         </is>
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>http://www.vershirevt.org</t>
+          <t>http://www.vergennes.org/</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
@@ -12894,7 +12894,7 @@
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>Victory</t>
+          <t>Vernon</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
@@ -12904,12 +12904,12 @@
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>Essex</t>
+          <t>Windham</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>ocd-jurisdiction/country:us/state:vt/place:victory/government</t>
+          <t>ocd-jurisdiction/country:us/state:vt/place:vernon/government</t>
         </is>
       </c>
       <c r="E235" t="inlineStr">
@@ -12941,7 +12941,7 @@
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>Waitsfield</t>
+          <t>Vershire</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
@@ -12951,17 +12951,17 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>Washington</t>
+          <t>Orange</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>ocd-jurisdiction/country:us/state:vt/place:waitsfield/government</t>
+          <t>ocd-jurisdiction/country:us/state:vt/place:vershire/government</t>
         </is>
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>Needs Research</t>
+          <t>http://www.vershirevt.org</t>
         </is>
       </c>
       <c r="F236" t="inlineStr">
@@ -12988,7 +12988,7 @@
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>Walden</t>
+          <t>Victory</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
@@ -12998,12 +12998,12 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>Caledonia</t>
+          <t>Essex</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>ocd-jurisdiction/country:us/state:vt/place:walden/government</t>
+          <t>ocd-jurisdiction/country:us/state:vt/place:victory/government</t>
         </is>
       </c>
       <c r="E237" t="inlineStr">
@@ -13035,7 +13035,7 @@
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>Wallingford</t>
+          <t>Waitsfield</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
@@ -13045,17 +13045,17 @@
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>Rutland</t>
+          <t>Washington</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>ocd-jurisdiction/country:us/state:vt/place:wallingford/government</t>
+          <t>ocd-jurisdiction/country:us/state:vt/place:waitsfield/government</t>
         </is>
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>http://www.wallingfordvt.com/</t>
+          <t>Needs Research</t>
         </is>
       </c>
       <c r="F238" t="inlineStr">
@@ -13082,7 +13082,7 @@
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>Waltham</t>
+          <t>Walden</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
@@ -13092,12 +13092,12 @@
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>Addison</t>
+          <t>Caledonia</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>ocd-jurisdiction/country:us/state:vt/place:waltham/government</t>
+          <t>ocd-jurisdiction/country:us/state:vt/place:walden/government</t>
         </is>
       </c>
       <c r="E239" t="inlineStr">
@@ -13129,7 +13129,7 @@
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>Wardsboro</t>
+          <t>Wallingford</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
@@ -13139,17 +13139,17 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>Windham</t>
+          <t>Rutland</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>ocd-jurisdiction/country:us/state:vt/place:wardsboro/government</t>
+          <t>ocd-jurisdiction/country:us/state:vt/place:wallingford/government</t>
         </is>
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>Needs Research</t>
+          <t>http://www.wallingfordvt.com/</t>
         </is>
       </c>
       <c r="F240" t="inlineStr">
@@ -13176,7 +13176,7 @@
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>Warren</t>
+          <t>Waltham</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
@@ -13186,17 +13186,17 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>Washington</t>
+          <t>Addison</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>ocd-jurisdiction/country:us/state:vt/place:warren/government</t>
+          <t>ocd-jurisdiction/country:us/state:vt/place:waltham/government</t>
         </is>
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>http://www.warrenvt.org</t>
+          <t>Needs Research</t>
         </is>
       </c>
       <c r="F241" t="inlineStr">
@@ -13223,7 +13223,7 @@
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>Washington</t>
+          <t>Wardsboro</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
@@ -13233,12 +13233,12 @@
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>Orange</t>
+          <t>Windham</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>ocd-jurisdiction/country:us/state:vt/place:washington/government</t>
+          <t>ocd-jurisdiction/country:us/state:vt/place:wardsboro/government</t>
         </is>
       </c>
       <c r="E242" t="inlineStr">
@@ -13270,7 +13270,7 @@
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>Waterbury</t>
+          <t>Warren</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
@@ -13285,12 +13285,12 @@
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>ocd-jurisdiction/country:us/state:vt/place:waterbury/government</t>
+          <t>ocd-jurisdiction/country:us/state:vt/place:warren/government</t>
         </is>
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>http://www.waterburyvt.com/</t>
+          <t>http://www.warrenvt.org</t>
         </is>
       </c>
       <c r="F243" t="inlineStr">
@@ -13317,7 +13317,7 @@
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Washington</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
@@ -13327,12 +13327,12 @@
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>Caledonia</t>
+          <t>Orange</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>ocd-jurisdiction/country:us/state:vt/place:waterford/government</t>
+          <t>ocd-jurisdiction/country:us/state:vt/place:washington/government</t>
         </is>
       </c>
       <c r="E244" t="inlineStr">
@@ -13364,7 +13364,7 @@
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>Waterville</t>
+          <t>Waterbury</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
@@ -13374,17 +13374,17 @@
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>Lamoille</t>
+          <t>Washington</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>ocd-jurisdiction/country:us/state:vt/place:waterville/government</t>
+          <t>ocd-jurisdiction/country:us/state:vt/place:waterbury/government</t>
         </is>
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>Needs Research</t>
+          <t>http://www.waterburyvt.com/</t>
         </is>
       </c>
       <c r="F245" t="inlineStr">
@@ -13411,7 +13411,7 @@
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>Weathersfield</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
@@ -13421,17 +13421,17 @@
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>Windsor</t>
+          <t>Caledonia</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>ocd-jurisdiction/country:us/state:vt/place:weathersfield/government</t>
+          <t>ocd-jurisdiction/country:us/state:vt/place:waterford/government</t>
         </is>
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>http://www.weathersfield.org/</t>
+          <t>Needs Research</t>
         </is>
       </c>
       <c r="F246" t="inlineStr">
@@ -13458,7 +13458,7 @@
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>Wells</t>
+          <t>Waterville</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
@@ -13468,17 +13468,17 @@
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>Rutland</t>
+          <t>Lamoille</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>ocd-jurisdiction/country:us/state:vt/place:wells/government</t>
+          <t>ocd-jurisdiction/country:us/state:vt/place:waterville/government</t>
         </is>
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>http://www.wellsvt.com</t>
+          <t>Needs Research</t>
         </is>
       </c>
       <c r="F247" t="inlineStr">
@@ -13505,27 +13505,27 @@
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>Wells River</t>
+          <t>Weathersfield</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>Village</t>
+          <t>Town</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>Orange</t>
+          <t>Windsor</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>ocd-jurisdiction/country:us/state:vt/place:wells-river/government</t>
+          <t>ocd-jurisdiction/country:us/state:vt/place:weathersfield/government</t>
         </is>
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>Needs Research</t>
+          <t>http://www.weathersfield.org/</t>
         </is>
       </c>
       <c r="F248" t="inlineStr">
@@ -13552,27 +13552,27 @@
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>West Burke</t>
+          <t>Wells</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>Village</t>
+          <t>Town</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>Caledonia</t>
+          <t>Rutland</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>ocd-jurisdiction/country:us/state:vt/place:west-burke/government</t>
+          <t>ocd-jurisdiction/country:us/state:vt/place:wells/government</t>
         </is>
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>Needs Research</t>
+          <t>http://www.wellsvt.com</t>
         </is>
       </c>
       <c r="F249" t="inlineStr">
@@ -13599,12 +13599,12 @@
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>West Fairlee</t>
+          <t>Wells River</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>Town</t>
+          <t>Village</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
@@ -13614,7 +13614,7 @@
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>ocd-jurisdiction/country:us/state:vt/place:west-fairlee/government</t>
+          <t>ocd-jurisdiction/country:us/state:vt/place:wells-river/government</t>
         </is>
       </c>
       <c r="E250" t="inlineStr">
@@ -13646,22 +13646,22 @@
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>West Haven</t>
+          <t>West Burke</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>Town</t>
+          <t>Village</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>Rutland</t>
+          <t>Caledonia</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>ocd-jurisdiction/country:us/state:vt/place:west-haven/government</t>
+          <t>ocd-jurisdiction/country:us/state:vt/place:west-burke/government</t>
         </is>
       </c>
       <c r="E251" t="inlineStr">
@@ -13693,7 +13693,7 @@
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>West Rutland</t>
+          <t>West Fairlee</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
@@ -13703,17 +13703,17 @@
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>Rutland</t>
+          <t>Orange</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>ocd-jurisdiction/country:us/state:vt/place:west-rutland/government</t>
+          <t>ocd-jurisdiction/country:us/state:vt/place:west-fairlee/government</t>
         </is>
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>http://www.westrutlandtown.com</t>
+          <t>Needs Research</t>
         </is>
       </c>
       <c r="F252" t="inlineStr">
@@ -13740,7 +13740,7 @@
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>West Windsor</t>
+          <t>West Haven</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
@@ -13750,17 +13750,17 @@
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>Windsor</t>
+          <t>Rutland</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>ocd-jurisdiction/country:us/state:vt/place:west-windsor/government</t>
+          <t>ocd-jurisdiction/country:us/state:vt/place:west-haven/government</t>
         </is>
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>http://www.westwindsorut.govoffice2.com</t>
+          <t>Needs Research</t>
         </is>
       </c>
       <c r="F253" t="inlineStr">
@@ -13787,7 +13787,7 @@
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>Westfield</t>
+          <t>West Rutland</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
@@ -13797,17 +13797,17 @@
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>Orleans</t>
+          <t>Rutland</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>ocd-jurisdiction/country:us/state:vt/place:westfield/government</t>
+          <t>ocd-jurisdiction/country:us/state:vt/place:west-rutland/government</t>
         </is>
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>Needs Research</t>
+          <t>http://www.westrutlandtown.com</t>
         </is>
       </c>
       <c r="F254" t="inlineStr">
@@ -13834,7 +13834,7 @@
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>Westford</t>
+          <t>West Windsor</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
@@ -13844,17 +13844,17 @@
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>Chittenden</t>
+          <t>Windsor</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>ocd-jurisdiction/country:us/state:vt/place:westford/government</t>
+          <t>ocd-jurisdiction/country:us/state:vt/place:west-windsor/government</t>
         </is>
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>http://www.westfordvt.us</t>
+          <t>http://www.westwindsorut.govoffice2.com</t>
         </is>
       </c>
       <c r="F255" t="inlineStr">
@@ -13881,27 +13881,27 @@
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>Westminster</t>
+          <t>Westbury</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>Town</t>
+          <t>Village</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>Windham</t>
+          <t>Chittenden</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>ocd-jurisdiction/country:us/state:vt/place:westminster-81400/government</t>
+          <t>ocd-jurisdiction/country:us/state:vt/place:westbury/government</t>
         </is>
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>http://www.westminster.govoffice.com</t>
+          <t>Needs Research</t>
         </is>
       </c>
       <c r="F256" t="inlineStr">
@@ -13921,29 +13921,29 @@
       </c>
       <c r="J256" t="inlineStr">
         <is>
-          <t>Seeded from repo jurisdiction file (Census 2022 Census of Governments). Charter chapter in Title 24 Appendix V.S.A. and code link to be backfilled from the Vermont Legislature municipal charters index and the official municipal website.</t>
+          <t>Added 2026-10-16 (issue #163 fix): missing from the Census 2022 seed; verified on the Vermont Secretary of State (VSARA) List of Incorporated Villages. Charter/code/website backfill as per sheet.</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>Westminster</t>
+          <t>Westfield</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>Village</t>
+          <t>Town</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>Windham</t>
+          <t>Orleans</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t>ocd-jurisdiction/country:us/state:vt/place:westminster/government</t>
+          <t>ocd-jurisdiction/country:us/state:vt/place:westfield/government</t>
         </is>
       </c>
       <c r="E257" t="inlineStr">
@@ -13975,7 +13975,7 @@
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>Westmore</t>
+          <t>Westford</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
@@ -13985,17 +13985,17 @@
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>Orleans</t>
+          <t>Chittenden</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>ocd-jurisdiction/country:us/state:vt/place:westmore/government</t>
+          <t>ocd-jurisdiction/country:us/state:vt/place:westford/government</t>
         </is>
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>http://www.westmoreonline.org</t>
+          <t>http://www.westfordvt.us</t>
         </is>
       </c>
       <c r="F258" t="inlineStr">
@@ -14022,7 +14022,7 @@
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>Weston</t>
+          <t>Westminster</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
@@ -14032,17 +14032,17 @@
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>Windsor</t>
+          <t>Windham</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>ocd-jurisdiction/country:us/state:vt/place:weston/government</t>
+          <t>ocd-jurisdiction/country:us/state:vt/place:westminster-81400/government</t>
         </is>
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>http://www.westonvt.org</t>
+          <t>http://www.westminster.govoffice.com</t>
         </is>
       </c>
       <c r="F259" t="inlineStr">
@@ -14069,27 +14069,27 @@
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>Weybridge</t>
+          <t>Westminster</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>Town</t>
+          <t>Village</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>Addison</t>
+          <t>Windham</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>ocd-jurisdiction/country:us/state:vt/place:weybridge/government</t>
+          <t>ocd-jurisdiction/country:us/state:vt/place:westminster/government</t>
         </is>
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>http://www.weybridge.govoffice.com</t>
+          <t>Needs Research</t>
         </is>
       </c>
       <c r="F260" t="inlineStr">
@@ -14116,7 +14116,7 @@
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>Wheelock</t>
+          <t>Westmore</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
@@ -14126,17 +14126,17 @@
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>Caledonia</t>
+          <t>Orleans</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>ocd-jurisdiction/country:us/state:vt/place:wheelock/government</t>
+          <t>ocd-jurisdiction/country:us/state:vt/place:westmore/government</t>
         </is>
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>Needs Research</t>
+          <t>http://www.westmoreonline.org</t>
         </is>
       </c>
       <c r="F261" t="inlineStr">
@@ -14163,7 +14163,7 @@
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>Whiting</t>
+          <t>Weston</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
@@ -14173,17 +14173,17 @@
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>Addison</t>
+          <t>Windsor</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>ocd-jurisdiction/country:us/state:vt/place:whiting/government</t>
+          <t>ocd-jurisdiction/country:us/state:vt/place:weston/government</t>
         </is>
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>Needs Research</t>
+          <t>http://www.westonvt.org</t>
         </is>
       </c>
       <c r="F262" t="inlineStr">
@@ -14210,7 +14210,7 @@
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>Whitingham</t>
+          <t>Weybridge</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
@@ -14220,17 +14220,17 @@
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>Windham</t>
+          <t>Addison</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t>ocd-jurisdiction/country:us/state:vt/place:whitingham/government</t>
+          <t>ocd-jurisdiction/country:us/state:vt/place:weybridge/government</t>
         </is>
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>Needs Research</t>
+          <t>http://www.weybridge.govoffice.com</t>
         </is>
       </c>
       <c r="F263" t="inlineStr">
@@ -14257,7 +14257,7 @@
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>Williamstown</t>
+          <t>Wheelock</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
@@ -14267,17 +14267,17 @@
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>Orange</t>
+          <t>Caledonia</t>
         </is>
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t>ocd-jurisdiction/country:us/state:vt/place:williamstown/government</t>
+          <t>ocd-jurisdiction/country:us/state:vt/place:wheelock/government</t>
         </is>
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>http://www.williamstowvt.org</t>
+          <t>Needs Research</t>
         </is>
       </c>
       <c r="F264" t="inlineStr">
@@ -14304,7 +14304,7 @@
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>Williston</t>
+          <t>Whiting</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
@@ -14314,17 +14314,17 @@
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>Chittenden</t>
+          <t>Addison</t>
         </is>
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t>ocd-jurisdiction/country:us/state:vt/place:williston/government</t>
+          <t>ocd-jurisdiction/country:us/state:vt/place:whiting/government</t>
         </is>
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t>http://town.williston.vt.us/</t>
+          <t>Needs Research</t>
         </is>
       </c>
       <c r="F265" t="inlineStr">
@@ -14351,7 +14351,7 @@
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>Wilmington</t>
+          <t>Whitingham</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
@@ -14366,7 +14366,7 @@
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t>ocd-jurisdiction/country:us/state:vt/place:wilmington/government</t>
+          <t>ocd-jurisdiction/country:us/state:vt/place:whitingham/government</t>
         </is>
       </c>
       <c r="E266" t="inlineStr">
@@ -14398,7 +14398,7 @@
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>Windham</t>
+          <t>Williamstown</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
@@ -14408,17 +14408,17 @@
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>Windham</t>
+          <t>Orange</t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>ocd-jurisdiction/country:us/state:vt/place:windham/government</t>
+          <t>ocd-jurisdiction/country:us/state:vt/place:williamstown/government</t>
         </is>
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>Needs Research</t>
+          <t>http://www.williamstowvt.org</t>
         </is>
       </c>
       <c r="F267" t="inlineStr">
@@ -14445,7 +14445,7 @@
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>Windsor</t>
+          <t>Williston</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
@@ -14455,17 +14455,17 @@
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>Windsor</t>
+          <t>Chittenden</t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t>ocd-jurisdiction/country:us/state:vt/place:windsor/government</t>
+          <t>ocd-jurisdiction/country:us/state:vt/place:williston/government</t>
         </is>
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>Needs Research</t>
+          <t>http://town.williston.vt.us/</t>
         </is>
       </c>
       <c r="F268" t="inlineStr">
@@ -14492,7 +14492,7 @@
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>Winhall</t>
+          <t>Wilmington</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
@@ -14502,17 +14502,17 @@
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>Bennington</t>
+          <t>Windham</t>
         </is>
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>ocd-jurisdiction/country:us/state:vt/place:winhall/government</t>
+          <t>ocd-jurisdiction/country:us/state:vt/place:wilmington/government</t>
         </is>
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>http://www.winhall.govoffice2.com</t>
+          <t>Needs Research</t>
         </is>
       </c>
       <c r="F269" t="inlineStr">
@@ -14539,27 +14539,27 @@
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>Winooski</t>
+          <t>Windham</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>City</t>
+          <t>Town</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>Chittenden</t>
+          <t>Windham</t>
         </is>
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t>ocd-jurisdiction/country:us/state:vt/place:winooski/government</t>
+          <t>ocd-jurisdiction/country:us/state:vt/place:windham/government</t>
         </is>
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>http://www.winooskivt.org</t>
+          <t>Needs Research</t>
         </is>
       </c>
       <c r="F270" t="inlineStr">
@@ -14586,7 +14586,7 @@
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>Wolcott</t>
+          <t>Windsor</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
@@ -14596,12 +14596,12 @@
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>Lamoille</t>
+          <t>Windsor</t>
         </is>
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t>ocd-jurisdiction/country:us/state:vt/place:wolcott/government</t>
+          <t>ocd-jurisdiction/country:us/state:vt/place:windsor/government</t>
         </is>
       </c>
       <c r="E271" t="inlineStr">
@@ -14633,7 +14633,7 @@
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>Woodbury</t>
+          <t>Winhall</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
@@ -14643,17 +14643,17 @@
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>Washington</t>
+          <t>Bennington</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t>ocd-jurisdiction/country:us/state:vt/place:woodbury/government</t>
+          <t>ocd-jurisdiction/country:us/state:vt/place:winhall/government</t>
         </is>
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>Needs Research</t>
+          <t>http://www.winhall.govoffice2.com</t>
         </is>
       </c>
       <c r="F272" t="inlineStr">
@@ -14680,27 +14680,27 @@
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>Woodford</t>
+          <t>Winooski</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>Town</t>
+          <t>City</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>Bennington</t>
+          <t>Chittenden</t>
         </is>
       </c>
       <c r="D273" t="inlineStr">
         <is>
-          <t>ocd-jurisdiction/country:us/state:vt/place:woodford/government</t>
+          <t>ocd-jurisdiction/country:us/state:vt/place:winooski/government</t>
         </is>
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>Needs Research</t>
+          <t>http://www.winooskivt.org</t>
         </is>
       </c>
       <c r="F273" t="inlineStr">
@@ -14727,7 +14727,7 @@
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>Woodstock</t>
+          <t>Wolcott</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
@@ -14737,17 +14737,17 @@
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>Windsor</t>
+          <t>Lamoille</t>
         </is>
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t>ocd-jurisdiction/country:us/state:vt/place:woodstock-85975/government</t>
+          <t>ocd-jurisdiction/country:us/state:vt/place:wolcott/government</t>
         </is>
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>http://www.townofwoodstock.org</t>
+          <t>Needs Research</t>
         </is>
       </c>
       <c r="F274" t="inlineStr">
@@ -14774,27 +14774,27 @@
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>Woodstock</t>
+          <t>Woodbury</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>Village</t>
+          <t>Town</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>Windsor</t>
+          <t>Washington</t>
         </is>
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t>ocd-jurisdiction/country:us/state:vt/place:woodstock/government</t>
+          <t>ocd-jurisdiction/country:us/state:vt/place:woodbury/government</t>
         </is>
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>http://www.townofwoodstock.org</t>
+          <t>Needs Research</t>
         </is>
       </c>
       <c r="F275" t="inlineStr">
@@ -14821,45 +14821,186 @@
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
+          <t>Woodford</t>
+        </is>
+      </c>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>Town</t>
+        </is>
+      </c>
+      <c r="C276" t="inlineStr">
+        <is>
+          <t>Bennington</t>
+        </is>
+      </c>
+      <c r="D276" t="inlineStr">
+        <is>
+          <t>ocd-jurisdiction/country:us/state:vt/place:woodford/government</t>
+        </is>
+      </c>
+      <c r="E276" t="inlineStr">
+        <is>
+          <t>Needs Research</t>
+        </is>
+      </c>
+      <c r="F276" t="inlineStr">
+        <is>
+          <t>Needs Research</t>
+        </is>
+      </c>
+      <c r="G276" t="inlineStr">
+        <is>
+          <t>Needs Research</t>
+        </is>
+      </c>
+      <c r="I276" t="inlineStr">
+        <is>
+          <t>Needs Research</t>
+        </is>
+      </c>
+      <c r="J276" t="inlineStr">
+        <is>
+          <t>Seeded from repo jurisdiction file (Census 2022 Census of Governments). Charter chapter in Title 24 Appendix V.S.A. and code link to be backfilled from the Vermont Legislature municipal charters index and the official municipal website.</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>Woodstock</t>
+        </is>
+      </c>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>Town</t>
+        </is>
+      </c>
+      <c r="C277" t="inlineStr">
+        <is>
+          <t>Windsor</t>
+        </is>
+      </c>
+      <c r="D277" t="inlineStr">
+        <is>
+          <t>ocd-jurisdiction/country:us/state:vt/place:woodstock-85975/government</t>
+        </is>
+      </c>
+      <c r="E277" t="inlineStr">
+        <is>
+          <t>http://www.townofwoodstock.org</t>
+        </is>
+      </c>
+      <c r="F277" t="inlineStr">
+        <is>
+          <t>Needs Research</t>
+        </is>
+      </c>
+      <c r="G277" t="inlineStr">
+        <is>
+          <t>Needs Research</t>
+        </is>
+      </c>
+      <c r="I277" t="inlineStr">
+        <is>
+          <t>Needs Research</t>
+        </is>
+      </c>
+      <c r="J277" t="inlineStr">
+        <is>
+          <t>Seeded from repo jurisdiction file (Census 2022 Census of Governments). Charter chapter in Title 24 Appendix V.S.A. and code link to be backfilled from the Vermont Legislature municipal charters index and the official municipal website.</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>Woodstock</t>
+        </is>
+      </c>
+      <c r="B278" t="inlineStr">
+        <is>
+          <t>Village</t>
+        </is>
+      </c>
+      <c r="C278" t="inlineStr">
+        <is>
+          <t>Windsor</t>
+        </is>
+      </c>
+      <c r="D278" t="inlineStr">
+        <is>
+          <t>ocd-jurisdiction/country:us/state:vt/place:woodstock/government</t>
+        </is>
+      </c>
+      <c r="E278" t="inlineStr">
+        <is>
+          <t>http://www.townofwoodstock.org</t>
+        </is>
+      </c>
+      <c r="F278" t="inlineStr">
+        <is>
+          <t>Needs Research</t>
+        </is>
+      </c>
+      <c r="G278" t="inlineStr">
+        <is>
+          <t>Needs Research</t>
+        </is>
+      </c>
+      <c r="I278" t="inlineStr">
+        <is>
+          <t>Needs Research</t>
+        </is>
+      </c>
+      <c r="J278" t="inlineStr">
+        <is>
+          <t>Seeded from repo jurisdiction file (Census 2022 Census of Governments). Charter chapter in Title 24 Appendix V.S.A. and code link to be backfilled from the Vermont Legislature municipal charters index and the official municipal website.</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
           <t>Worcester</t>
         </is>
       </c>
-      <c r="B276" t="inlineStr">
-        <is>
-          <t>Town</t>
-        </is>
-      </c>
-      <c r="C276" t="inlineStr">
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>Town</t>
+        </is>
+      </c>
+      <c r="C279" t="inlineStr">
         <is>
           <t>Washington</t>
         </is>
       </c>
-      <c r="D276" t="inlineStr">
+      <c r="D279" t="inlineStr">
         <is>
           <t>ocd-jurisdiction/country:us/state:vt/place:worcester/government</t>
         </is>
       </c>
-      <c r="E276" t="inlineStr">
-        <is>
-          <t>Needs Research</t>
-        </is>
-      </c>
-      <c r="F276" t="inlineStr">
-        <is>
-          <t>Needs Research</t>
-        </is>
-      </c>
-      <c r="G276" t="inlineStr">
-        <is>
-          <t>Needs Research</t>
-        </is>
-      </c>
-      <c r="I276" t="inlineStr">
-        <is>
-          <t>Needs Research</t>
-        </is>
-      </c>
-      <c r="J276" t="inlineStr">
+      <c r="E279" t="inlineStr">
+        <is>
+          <t>Needs Research</t>
+        </is>
+      </c>
+      <c r="F279" t="inlineStr">
+        <is>
+          <t>Needs Research</t>
+        </is>
+      </c>
+      <c r="G279" t="inlineStr">
+        <is>
+          <t>Needs Research</t>
+        </is>
+      </c>
+      <c r="I279" t="inlineStr">
+        <is>
+          <t>Needs Research</t>
+        </is>
+      </c>
+      <c r="J279" t="inlineStr">
         <is>
           <t>Seeded from repo jurisdiction file (Census 2022 Census of Governments). Charter chapter in Title 24 Appendix V.S.A. and code link to be backfilled from the Vermont Legislature municipal charters index and the official municipal website.</t>
         </is>
@@ -15713,7 +15854,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>28 incorporated villages.</t>
+          <t>31 active incorporated villages (SOS/VSARA list).</t>
         </is>
       </c>
     </row>
@@ -15926,7 +16067,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H9"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="44" customWidth="1" min="1" max="1"/>
@@ -16009,7 +16150,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Enumeration of VT general-purpose governments seeded into repo jurisdiction files (275 municipal + 14 county).</t>
+          <t>Enumeration of VT general-purpose governments seeded into repo jurisdiction files (275 municipal + 14 county at seed time; corrected 2026-10-16 -- see Status Log).</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -16019,7 +16160,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Municipality / county mapping and websites in this workbook come from those repo files.</t>
+          <t>Municipality / county mapping and websites in this workbook come from those repo files. The seed is stale in four places and wrong-by-omission in one more (Lyndonville merger) -- all corrected from official state sources on 2026-10-16.</t>
         </is>
       </c>
     </row>
@@ -16224,12 +16365,12 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>USED -- cross-check of the 275 repo jurisdictions</t>
+          <t>USED -- cross-check of the repo jurisdictions</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Association, not government: use to locate/verify official sources, never as source of record (the MS MML rule). COUNT DRIFT FLAGGED 2026-10-16: VLCT totals also sum to 275 (237 towns + 10 cities + 28 villages) but the repo Census 2022 seed splits as 235 towns + 10 cities + 30 villages. Two places are classified differently between the two sources; identify them in backfill before treating either split as final.</t>
+          <t>Association, not government: use to locate/verify official sources, never as source of record (the MS MML rule). COUNT RECONCILIATION RESOLVED 2026-10-16: VLCT's town count (237) proved right and its village count (28) still differs by 3 from the SOS-governed active count (31); the Census seed's split (235 towns / 30 villages) was stale, not differently classified -- see Status Log.</t>
         </is>
       </c>
     </row>
@@ -16314,6 +16455,132 @@
       <c r="H9" t="inlineStr">
         <is>
           <t>Do not mint probate posts until this enumeration is in hand.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Vermont.gov -- Towns &amp; Cities explorer</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Municipal</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Official (state)</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Scrape / manual</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>https://www.vermont.gov/towns-and-Cities</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>The state portal's per-town/city entries: county, census population, land area, town clerk, website. Covers towns and cities (plus gores/grants) -- NOT incorporated villages.</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>USED -- municipality reconciliation (2026-10-16)</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Source of record for the town/city universe; verified Bloomfield and Sudbury, missing from the Census 2022 seed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Vermont Secretary of State (VSARA) -- List of Incorporated Villages</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Municipal</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Official (state)</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Scrape / manual</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>https://sos.vermont.gov/vsara/learn/municipalities/incorporated-villages</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>The official village universe: 33 villages named with parent town/county and incorporation citation; Groton and Townshend flagged inactive on the page itself.</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>USED -- village reconciliation (2026-10-16)</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Governs the village count (31 active). Added Jericho (1933) and Westbury (2023) to the repo; Lyndonville absent from the current page, consistent with its merger.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Vermont General Assembly -- H.490 bill status (Act M-14)</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Municipal</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Official (state)</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Manual</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>https://legislature.vermont.gov/bill/status/2024/H.490</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Merger of the Village of Lyndonville with the Town of Lyndon: voter approval 2022-11-08, Governor approval 2023-06-19; Town of Lyndon charter at 24 App. V.S.A. chapter 126.</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>USED -- Lyndonville retirement (2026-10-16)</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Basis for deleting the Lyndonville jurisdiction and noting the merger on the Town of Lyndon record.</t>
         </is>
       </c>
     </row>
@@ -16328,7 +16595,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:E3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -16373,7 +16640,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Created workbook for issue #163. Government Structure determined from the Vermont Constitution and Titles 17/24 (town-meeting state; counties are judicial/law-enforcement units whose only elected officers are State's Attorney, Sheriff, Assistant Judges x2, Judge of Probate, and High Bailiff; county clerk and treasurer are appointed). Municipalities seeded with all 275 repo jurisdictions (237 towns, 10 cities, 28 incorporated villages; VLCT's current split is 237 towns / 28 villages -- same 275 total, two-place classification drift flagged in Sources). Counties seeded (14). State executive posts (6) and county posts (56 posts / 70 seats) built in the repo by scripts/build_vt_state_county_posts.py; validation PASSED, 0 errors (5 pre-existing federal no-election-trace warnings). HELD: probate posts (18 districts, not 14), legislative districts (House 150 / Senate 30), all memberships, school districts, UTG.</t>
+          <t>Created workbook for issue #163. Government Structure determined from the Vermont Constitution and Titles 17/24 (town-meeting state; counties are judicial/law-enforcement units whose only elected officers are State's Attorney, Sheriff, Assistant Judges x2, Judge of Probate, and High Bailiff; county clerk and treasurer are appointed). Municipalities seeded with all 275 repo jurisdictions (Census 2022 split: 235 towns, 10 cities, 30 incorporated villages; VLCT's current split is 237 towns / 28 villages -- same 275 total, two-place classification drift flagged in Sources). Counties seeded (14). State executive posts (6) and county posts (56 posts / 70 seats) built in the repo by scripts/build_vt_state_county_posts.py; validation PASSED, 0 errors (5 pre-existing federal no-election-trace warnings). HELD: probate posts (18 districts, not 14), legislative districts (House 150 / Senate 30), all memberships, school districts, UTG.</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -16387,6 +16654,33 @@
         </is>
       </c>
       <c r="E2" t="inlineStr">
+        <is>
+          <t>CivicMirror</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Municipality reconciliation fix (same day, at Walter's direction). A name-level diff against the VT Jurisdiction Factory (276) plus official verification settled the count drift: (1) Town of Bloomfield (Essex Co.) and Town of Sudbury (Rutland Co.) were missing from the Census 2022 seed entirely -- both verified on the official Vermont.gov Towns &amp; Cities explorer and added as jurisdictions. (2) Village of Jericho (Act 12, Special Session 1933) and Village of Westbury (Colchester, 2023) were missing from BOTH the seed and the factory -- added from the SOS/VSARA List of Incorporated Villages. (3) Village of Lyndonville was retired: merged into the Town of Lyndon by Act M-14 (H.490; voters 2022-11-08, Governor 2023-06-19; charter at 24 App. ch. 126), noted on the Lyndon record. Groton and Townshend villages were NOT added (SOS flags both inactive). New totals: 278 municipal jurisdictions (237 towns / 10 cities / 31 active villages). Towns now reconcile exactly across Census-corrected repo, factory, and VLCT (237); VLCT's village headline (28) remains 3 below the SOS-governed 31, definitional, unresolved in its document.</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Municipalities, Sources, Government Structure, Office Titles (Ref)</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Vermont.gov Towns &amp; Cities explorer; SOS/VSARA List of Incorporated Villages; VT General Assembly H.490 (Act M-14); VLCT municipal counts (cross-check)</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
         <is>
           <t>CivicMirror</t>
         </is>

--- a/reference/VT Rolling Audit/VT_Municipalities.xlsx
+++ b/reference/VT Rolling Audit/VT_Municipalities.xlsx
@@ -3044,27 +3044,27 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Needs Research</t>
+          <t>None (no official town website)</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Needs Research</t>
+          <t>None (general law; no Title 24 Appendix chapter)</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Needs Research</t>
+          <t>None published</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Needs Research</t>
+          <t>Roster backfilled 2026-10-16</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>Added 2026-10-16 (issue #163 fix): missing from the Census 2022 seed; verified on the official Vermont.gov Towns &amp; Cities explorer. Charter/code/website backfill as per sheet.</t>
+          <t>Added 2026-10-16 (issue #163 fix): missing from the Census 2022 seed; verified on the official Vermont.gov Towns &amp; Cities explorer. Municipal sweep completed 2026-10-16 (worked example, tracking PR #168): Selectboard, Town Treasurer, and Justices of the Peace backfilled from SOS Elections Division directories; November 5, 2024 JP election record built. Town Clerk holder HELD (SOS guide, SOS contact spreadsheet, and Vermont.gov explorer name three different people). Lesser town officers await the printed town report or a clerk reply. No charter (general law), no official website, no published code.</t>
         </is>
       </c>
     </row>
@@ -16595,7 +16595,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3"/>
+  <dimension ref="A1:E4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -16686,6 +16686,33 @@
         </is>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Bloomfield municipal sweep -- worked example for the VT municipal tier (tracking PR #168). Roster backfilled from SOS Elections Division directories: Selectboard -- Eric Brault, Josh Riley, Denault Routhier (SOS selectboard directory, June 5, 2026); Town Treasurer -- Sharon Belknap (SOS treasurer contact spreadsheet, June 12, 2026, corroborated by the SOS clerk guide, January 2026); Justices of the Peace x5 -- Ray Bowen, Sharon Belknap, Bryant Wheeler, Suzanne Routhier, Steven Bunnell (SOS '2025-2026 Vermont Justices of the Peace' listing, December 4, 2025), with the November 5, 2024 JP election record built from the same listing (vote totals not published there and not recorded). Town Clerk membership HELD: the SOS guide (January 2026) names Susan Robidas, the SOS clerk contact spreadsheet (June 2026) names Ray Bowen, and the Vermont.gov explorer names Paulette Routhier -- post created, holder awaits a tiebreak. Moderator, Listers, Auditors, Constables, Grand Juror, and Town Agent were NOT minted: no official online source names Bloomfield's holders (no town website; the printed annual town report is not posted). Charter: none -- no Title 24 Appendix chapter (general-law town, full index checked); no official website; no published municipal code. Factory concordance: the VT Jurisdiction Factory carries Selectboard only for Bloomfield and matches name-for-name; every other office is outside its bounded scope.</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Municipalities (Bloomfield row), Status Log</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>VT SOS Elections Division directories (selectboard directory; clerk/treasurer contact spreadsheets; JP listing); Title 24 Appendix chapter index (Vermont Statutes Online)</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>CivicMirror</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/reference/VT Rolling Audit/VT_Municipalities.xlsx
+++ b/reference/VT Rolling Audit/VT_Municipalities.xlsx
@@ -3064,7 +3064,7 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>Added 2026-10-16 (issue #163 fix): missing from the Census 2022 seed; verified on the official Vermont.gov Towns &amp; Cities explorer. Municipal sweep completed 2026-10-16 (worked example, tracking PR #168): Selectboard, Town Treasurer, and Justices of the Peace backfilled from SOS Elections Division directories; November 5, 2024 JP election record built. Town Clerk holder HELD (SOS guide, SOS contact spreadsheet, and Vermont.gov explorer name three different people). Lesser town officers await the printed town report or a clerk reply. No charter (general law), no official website, no published code.</t>
+          <t>Added 2026-10-16 (issue #163 fix): missing from the Census 2022 seed; verified on the official Vermont.gov Towns &amp; Cities explorer. Municipal sweep completed 2026-10-16 (worked example, tracking PR #168): Selectboard, Town Treasurer, and Justices of the Peace backfilled from SOS Elections Division directories; November 5, 2024 JP election record built. Town Clerk resolved to Ray Bowen (SOS clerk contact spreadsheet, June 2026; the SOS guide's Robidas and the explorer's Routhier listings are stale vintages). Lesser town officers await the printed town report or a clerk reply. No charter (general law), no official website, no published code.</t>
         </is>
       </c>
     </row>
@@ -16595,7 +16595,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E4"/>
+  <dimension ref="A1:E5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -16713,6 +16713,33 @@
         </is>
       </c>
     </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Bloomfield Town Clerk resolved (follow-up to the sweep entry above; tracking PR #168). News/directory check at Walter's request, most recent first: Vermont Attorneys Title clerk directory (data obtained September 1, 2026) names Ray Bowen; the SOS clerk contact spreadsheet (June 12, 2026) names Ray Bowen; the North Star Monthly clerk directory (updated ~April 2026) and the SOS guide (January 2026) name Susan Robidas; VPIRG's clerk list (~2022) names Paulette Routhier -- the vintage the Vermont.gov explorer still carries. No news article covers the change. Walter directed minting Bowen on 2026-10-16: clerk membership added (Bowen already held a Justice of the Peace seat on the same person record). Robidas held the office into early 2026; Routhier's listing is a ~2022 artifact.</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Municipalities (Bloomfield row), Status Log</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>VT SOS clerk contact spreadsheet (June 12, 2026); Vermont Attorneys Title town clerk directory (September 1, 2026); North Star Monthly Kingdom Guide clerk directory; VPIRG clerk list (~2022)</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>CivicMirror</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/reference/VT Rolling Audit/VT_Municipalities.xlsx
+++ b/reference/VT Rolling Audit/VT_Municipalities.xlsx
@@ -3064,7 +3064,7 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>Added 2026-10-16 (issue #163 fix): missing from the Census 2022 seed; verified on the official Vermont.gov Towns &amp; Cities explorer. Municipal sweep completed 2026-10-16 (worked example, tracking PR #168): Selectboard, Town Treasurer, and Justices of the Peace backfilled from SOS Elections Division directories; November 5, 2024 JP election record built. Town Clerk resolved to Ray Bowen (SOS clerk contact spreadsheet, June 2026; the SOS guide's Robidas and the explorer's Routhier listings are stale vintages). Lesser town officers await the printed town report or a clerk reply. No charter (general law), no official website, no published code.</t>
+          <t>Added 2026-10-16 (issue #163 fix): missing from the Census 2022 seed; verified on the official Vermont.gov Towns &amp; Cities explorer. Municipal sweep completed 2026-10-16 (worked example, tracking PR #168): Selectboard, Town Treasurer, and Justices of the Peace backfilled from SOS Elections Division directories; November 5, 2024 JP election record built. Town Clerk resolved to Ray Bowen (SOS clerk contact spreadsheet, June 2026; the SOS guide's Robidas and the explorer's Routhier listings are stale vintages). Lesser town offices (Moderator, Listers x3, Auditors x3, Grand Juror, Town Agent) created as structure-only posts from 17 V.S.A. section 2646; holders await the printed town report or a clerk reply. Constable and Collector of Delinquent Taxes posts not created (per-town variations unverifiable). No charter (general law), no official website, no published code.</t>
         </is>
       </c>
     </row>
@@ -16595,7 +16595,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E5"/>
+  <dimension ref="A1:E6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -16740,6 +16740,33 @@
         </is>
       </c>
     </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Bloomfield data set completed as far as available information allows (tracking PR #168; supersedes the sweep entry's 'not minted' note for five of the six lesser offices). The five remaining section 2646 town offices - Moderator (1 seat), Listers (3), Auditors (3), Grand Juror (1), Town Agent (1) - were created as structure-only posts from 17 V.S.A. section 2646, the posts-first pattern used for the state and county build. No official source publishes Bloomfield's current holders for these offices, so memberships await the printed annual town report or a clerk records reply. Constable and Collector of Delinquent Taxes posts were NOT created: a post requires a seat count, towns elect one or two constables by local vote, and the collector is the treasurer ex officio unless the town votes to elect one separately (section 2651d) - both unverifiable from published sources. A final sweep of the VT Jurisdiction Factory confirmed it carries Bloomfield selectboard data only. Bloomfield totals in the repo: 9 posts, 10 memberships, 8 people, 1 election record.</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Municipalities (Bloomfield row), Status Log</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>17 V.S.A. sections 2646, 2649, 2651, 2651b, 2651d (Vermont Statutes Online); VT Jurisdiction Factory v0.1 (coverage re-check 2026-10-16)</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>CivicMirror</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
